--- a/mrg.xlsx
+++ b/mrg.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawu01\Desktop\md\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257AE883-1860-4292-965A-447B5B8E3484}" xr6:coauthVersionLast="33" xr6:coauthVersionMax="33" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B90453-2795-49A7-803A-80D1662E5273}" xr6:coauthVersionLast="33" xr6:coauthVersionMax="33" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" tabRatio="868" activeTab="5" xr2:uid="{39627F01-7337-4F89-8A01-1D6EB359A865}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" tabRatio="868" firstSheet="6" activeTab="15" xr2:uid="{39627F01-7337-4F89-8A01-1D6EB359A865}"/>
   </bookViews>
   <sheets>
     <sheet name="v0" sheetId="1" r:id="rId1"/>
-    <sheet name="PMF c0 round0" sheetId="3" r:id="rId2"/>
-    <sheet name="264PMF Y c0 round0" sheetId="20" r:id="rId3"/>
-    <sheet name="264PMF Y c1 round0" sheetId="21" r:id="rId4"/>
-    <sheet name="264PMF UV c0 round0" sheetId="24" r:id="rId5"/>
-    <sheet name="264PMF UV c1 round0" sheetId="25" r:id="rId6"/>
+    <sheet name="264PMF Y c0 round0" sheetId="20" r:id="rId2"/>
+    <sheet name="264PMF Y c1 round0" sheetId="21" r:id="rId3"/>
+    <sheet name="264PMF UV c0 round0" sheetId="24" r:id="rId4"/>
+    <sheet name="264PMF UV c1 round0" sheetId="25" r:id="rId5"/>
+    <sheet name="PMF c0 round0" sheetId="3" r:id="rId6"/>
     <sheet name="PMF sp c0 round0" sheetId="12" r:id="rId7"/>
     <sheet name="PMF sp c0 round1-3" sheetId="14" r:id="rId8"/>
     <sheet name="PMF c0 round1-3" sheetId="4" r:id="rId9"/>
@@ -28,6 +28,7 @@
     <sheet name="PMF UV c0 round1-3" sheetId="13" r:id="rId13"/>
     <sheet name="PMF UV c1 round0" sheetId="17" r:id="rId14"/>
     <sheet name="PMF UV c1 round1-3" sheetId="11" r:id="rId15"/>
+    <sheet name="Sheet21" sheetId="27" r:id="rId16"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="339">
   <si>
     <t>tile</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -811,6 +812,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>PMF_M8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMF_F8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>264PMF c0 round0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -968,13 +977,289 @@
   </si>
   <si>
     <t>PMF_F4_3</t>
+  </si>
+  <si>
+    <t>pixel 读取接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y c0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pixel 需求个数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pixel 读取个数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2x15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y c0  16*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y c0  8*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2x32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ram 颗粒度(pixel)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y c1  16*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uv c0  8*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uv c0  4*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uv c1  8*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2x16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2x7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">总结： Y 需要 4片 16x1 ram; UV 需要4片 8x1 ram; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMF_M16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMF_F16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以112*112 空间统计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总需求pixel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ram 片 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ram深度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chanel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ram 宽度（pixel)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ram 宽度 (pixel)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y c1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能利用复用节省</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uv c0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uv c1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输出缓存 （单口，独享）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本用满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能可以缩减深度到16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入REF PIXEL RAM (单口，独享，每拍输入）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输出block 顺序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8x8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16x16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4x4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8x2  -0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4x4  -0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32x32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16x1 -0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16x1 -32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8x1 -0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8x1 -16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4x4 channel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H264</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凑两笔输出 8x2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凑4笔输出 4x4 channel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>U 8x1 -0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V 8x1 -0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4x2 U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4x2 V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8x8 channel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8x2  -8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重组输出顺序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原始输出顺序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">64x64 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以4个独立的 32x32 计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">32x32 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以4个独立的16x16 计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16x1 -1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1067,8 +1352,17 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1083,12 +1377,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1309,6 +1615,19 @@
         <color rgb="FFDEE0E3"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1336,13 +1655,141 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1457,10 +1904,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1484,7 +1937,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1505,22 +1961,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1529,7 +1985,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1850,6 +2393,8 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="13.375" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="13" max="13" width="10.25" customWidth="1"/>
   </cols>
@@ -3449,13 +3994,13 @@
       <c r="U37" s="4"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A38" s="43" t="s">
+      <c r="A38" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="B38" s="44"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -3474,22 +4019,22 @@
       <c r="U38" s="4"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A39" s="48" t="s">
+      <c r="A39" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="B39" s="45" t="s">
+      <c r="B39" s="47" t="s">
         <v>182</v>
       </c>
-      <c r="C39" s="45" t="s">
+      <c r="C39" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="47" t="s">
         <v>185</v>
       </c>
-      <c r="F39" s="38"/>
+      <c r="F39" s="39"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -3507,23 +4052,23 @@
       <c r="U39" s="4"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A40" s="41" t="s">
+      <c r="A40" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="B40" s="42">
+      <c r="B40" s="44">
         <v>128</v>
       </c>
-      <c r="C40" s="46">
+      <c r="C40" s="48">
         <v>1</v>
       </c>
-      <c r="D40" s="40">
+      <c r="D40" s="42">
         <v>4</v>
       </c>
-      <c r="E40" s="40">
+      <c r="E40" s="42">
         <f>B40*C40*D40</f>
         <v>512</v>
       </c>
-      <c r="F40" s="38"/>
+      <c r="F40" s="39"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -3541,23 +4086,23 @@
       <c r="U40" s="4"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A41" s="45" t="s">
+      <c r="A41" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="40">
+      <c r="B41" s="42">
         <v>256</v>
       </c>
-      <c r="C41" s="40">
+      <c r="C41" s="42">
         <v>1</v>
       </c>
-      <c r="D41" s="40">
+      <c r="D41" s="42">
         <v>4</v>
       </c>
-      <c r="E41" s="40">
+      <c r="E41" s="42">
         <f>B41*C41*D41</f>
         <v>1024</v>
       </c>
-      <c r="F41" s="38"/>
+      <c r="F41" s="39"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -3575,17 +4120,17 @@
       <c r="U41" s="4"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A42" s="45" t="s">
+      <c r="A42" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="B42" s="40"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="48">
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="51">
         <f>SUM(E40:E41)</f>
         <v>1536</v>
       </c>
-      <c r="F42" s="38"/>
+      <c r="F42" s="39"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -3603,11 +4148,11 @@
       <c r="U42" s="4"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A43" s="47"/>
-      <c r="B43" s="47"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -3626,14 +4171,14 @@
       <c r="U43" s="4"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A44" s="48" t="s">
+      <c r="A44" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="38"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="39"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -3651,19 +4196,19 @@
       <c r="U44" s="4"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A45" s="41" t="s">
+      <c r="A45" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="B45" s="42">
+      <c r="B45" s="44">
         <v>64</v>
       </c>
-      <c r="C45" s="46">
+      <c r="C45" s="48">
         <v>4</v>
       </c>
-      <c r="D45" s="40">
+      <c r="D45" s="42">
         <v>4</v>
       </c>
-      <c r="E45" s="40">
+      <c r="E45" s="42">
         <f>B45*C45*D45</f>
         <v>1024</v>
       </c>
@@ -3685,19 +4230,19 @@
       <c r="U45" s="4"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A46" s="45" t="s">
+      <c r="A46" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="B46" s="40">
+      <c r="B46" s="42">
         <v>32</v>
       </c>
-      <c r="C46" s="40">
+      <c r="C46" s="42">
         <v>4</v>
       </c>
-      <c r="D46" s="40">
+      <c r="D46" s="42">
         <v>2</v>
       </c>
-      <c r="E46" s="40">
+      <c r="E46" s="42">
         <f t="shared" ref="E46" si="7">B46*C46*D46</f>
         <v>256</v>
       </c>
@@ -3719,13 +4264,13 @@
       <c r="U46" s="4"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A47" s="45" t="s">
+      <c r="A47" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="B47" s="40"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="40"/>
-      <c r="E47" s="48">
+      <c r="B47" s="42"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="51">
         <f>SUM(E45:E46)</f>
         <v>1280</v>
       </c>
@@ -3747,11 +4292,11 @@
       <c r="U47" s="4"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A48" s="44"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
+      <c r="A48" s="46"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -3770,14 +4315,14 @@
       <c r="U48" s="4"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A49" s="48" t="s">
+      <c r="A49" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="38"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="39"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -3795,23 +4340,23 @@
       <c r="U49" s="4"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A50" s="41" t="s">
+      <c r="A50" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="B50" s="42">
+      <c r="B50" s="44">
         <v>16</v>
       </c>
-      <c r="C50" s="46">
+      <c r="C50" s="48">
         <v>16</v>
       </c>
-      <c r="D50" s="40">
+      <c r="D50" s="42">
         <v>2</v>
       </c>
-      <c r="E50" s="40">
+      <c r="E50" s="42">
         <f t="shared" ref="E50:E52" si="8">B50*C50*D50</f>
         <v>512</v>
       </c>
-      <c r="F50" s="38"/>
+      <c r="F50" s="39"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -3829,19 +4374,19 @@
       <c r="U50" s="4"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A51" s="45" t="s">
+      <c r="A51" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="B51" s="40">
+      <c r="B51" s="42">
         <v>4</v>
       </c>
-      <c r="C51" s="40">
+      <c r="C51" s="42">
         <v>16</v>
       </c>
-      <c r="D51" s="40">
+      <c r="D51" s="42">
         <v>2</v>
       </c>
-      <c r="E51" s="40">
+      <c r="E51" s="42">
         <f t="shared" si="8"/>
         <v>128</v>
       </c>
@@ -3863,19 +4408,19 @@
       <c r="U51" s="4"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A52" s="45" t="s">
+      <c r="A52" s="47" t="s">
         <v>180</v>
       </c>
-      <c r="B52" s="40">
+      <c r="B52" s="42">
         <v>4</v>
       </c>
-      <c r="C52" s="40">
+      <c r="C52" s="42">
         <v>16</v>
       </c>
-      <c r="D52" s="40">
+      <c r="D52" s="42">
         <v>2</v>
       </c>
-      <c r="E52" s="48">
+      <c r="E52" s="51">
         <f t="shared" si="8"/>
         <v>128</v>
       </c>
@@ -3897,13 +4442,13 @@
       <c r="U52" s="4"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A53" s="45" t="s">
+      <c r="A53" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="45">
+      <c r="B53" s="47"/>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47">
         <f>SUM(E50:E52)</f>
         <v>768</v>
       </c>
@@ -3948,13 +4493,13 @@
       <c r="U54" s="4"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A55" s="48" t="s">
+      <c r="A55" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="45"/>
+      <c r="B55" s="47"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -3973,19 +4518,19 @@
       <c r="U55" s="4"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A56" s="41" t="s">
+      <c r="A56" s="43" t="s">
         <v>174</v>
       </c>
-      <c r="B56" s="42">
+      <c r="B56" s="44">
         <v>4</v>
       </c>
-      <c r="C56" s="46">
+      <c r="C56" s="48">
         <v>72</v>
       </c>
-      <c r="D56" s="40">
+      <c r="D56" s="42">
         <v>2</v>
       </c>
-      <c r="E56" s="40">
+      <c r="E56" s="42">
         <f t="shared" ref="E56:E57" si="9">B56*C56*D56</f>
         <v>576</v>
       </c>
@@ -4007,19 +4552,19 @@
       <c r="U56" s="4"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A57" s="45" t="s">
+      <c r="A57" s="47" t="s">
         <v>175</v>
       </c>
-      <c r="B57" s="40">
+      <c r="B57" s="42">
         <v>4</v>
       </c>
-      <c r="C57" s="40">
+      <c r="C57" s="42">
         <v>72</v>
       </c>
-      <c r="D57" s="40">
+      <c r="D57" s="42">
         <v>2</v>
       </c>
-      <c r="E57" s="40">
+      <c r="E57" s="42">
         <f t="shared" si="9"/>
         <v>576</v>
       </c>
@@ -4041,13 +4586,13 @@
       <c r="U57" s="4"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A58" s="45" t="s">
+      <c r="A58" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="B58" s="40"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="48">
+      <c r="B58" s="42"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="51">
         <f>SUM(E56:E57)</f>
         <v>1152</v>
       </c>
@@ -4102,42 +4647,42 @@
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
-      <c r="K60" s="39"/>
-      <c r="L60" s="39"/>
-      <c r="M60" s="39"/>
-      <c r="N60" s="39"/>
-      <c r="O60" s="39"/>
-      <c r="P60" s="39"/>
-      <c r="Q60" s="39"/>
-      <c r="R60" s="39"/>
+      <c r="K60" s="40"/>
+      <c r="L60" s="40"/>
+      <c r="M60" s="40"/>
+      <c r="N60" s="40"/>
+      <c r="O60" s="40"/>
+      <c r="P60" s="40"/>
+      <c r="Q60" s="40"/>
+      <c r="R60" s="40"/>
       <c r="S60" s="4"/>
       <c r="T60" s="4"/>
       <c r="U60" s="4"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A61" s="56" t="s">
+      <c r="A61" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-      <c r="H61" s="57"/>
-      <c r="I61" s="58"/>
-      <c r="J61" s="59"/>
-      <c r="K61" s="60" t="s">
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="60"/>
+      <c r="H61" s="60"/>
+      <c r="I61" s="61"/>
+      <c r="J61" s="62"/>
+      <c r="K61" s="63" t="s">
         <v>218</v>
       </c>
-      <c r="L61" s="60"/>
-      <c r="M61" s="60"/>
-      <c r="N61" s="60"/>
-      <c r="O61" s="60"/>
-      <c r="P61" s="60"/>
-      <c r="Q61" s="60"/>
-      <c r="R61" s="60"/>
-      <c r="S61" s="38"/>
+      <c r="L61" s="63"/>
+      <c r="M61" s="63"/>
+      <c r="N61" s="63"/>
+      <c r="O61" s="63"/>
+      <c r="P61" s="63"/>
+      <c r="Q61" s="63"/>
+      <c r="R61" s="63"/>
+      <c r="S61" s="39"/>
       <c r="T61" s="4"/>
       <c r="U61" s="4"/>
     </row>
@@ -4170,7 +4715,7 @@
         <v>18</v>
       </c>
       <c r="P62" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q62" t="s">
         <v>15</v>
@@ -4421,11 +4966,11 @@
         <v>25</v>
       </c>
       <c r="O68" s="4"/>
-      <c r="P68" s="56" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q68" s="54"/>
-      <c r="R68" s="55"/>
+      <c r="P68" s="59" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q68" s="57"/>
+      <c r="R68" s="58"/>
       <c r="S68" s="4"/>
       <c r="T68" s="4"/>
       <c r="U68" s="4"/>
@@ -4449,9 +4994,21 @@
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
+      <c r="K69">
+        <v>2</v>
+      </c>
+      <c r="L69">
+        <v>22</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>20</v>
+      </c>
       <c r="O69" s="4"/>
       <c r="P69" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q69" t="s">
         <v>15</v>
@@ -4865,19 +5422,19 @@
       <c r="U80" s="4"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4"/>
-      <c r="M81" s="4"/>
+      <c r="A81" s="40"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="40"/>
+      <c r="H81" s="40"/>
+      <c r="I81" s="40"/>
+      <c r="J81" s="40"/>
+      <c r="K81" s="40"/>
+      <c r="L81" s="40"/>
+      <c r="M81" s="40"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
       <c r="P81" s="4"/>
@@ -4888,20 +5445,22 @@
       <c r="U81" s="4"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
+      <c r="A82" s="71" t="s">
+        <v>306</v>
+      </c>
+      <c r="B82" s="71"/>
+      <c r="C82" s="71"/>
+      <c r="D82" s="71"/>
+      <c r="E82" s="71"/>
+      <c r="F82" s="71"/>
+      <c r="G82" s="71"/>
+      <c r="H82" s="71"/>
+      <c r="I82" s="71"/>
+      <c r="J82" s="71"/>
+      <c r="K82" s="71"/>
+      <c r="L82" s="71"/>
+      <c r="M82" s="71"/>
+      <c r="N82" s="39"/>
       <c r="O82" s="4"/>
       <c r="P82" s="4"/>
       <c r="Q82" s="4"/>
@@ -4911,20 +5470,20 @@
       <c r="U82" s="4"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
-      <c r="L83" s="4"/>
-      <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
+      <c r="A83" s="71"/>
+      <c r="B83" s="71"/>
+      <c r="C83" s="71"/>
+      <c r="D83" s="71"/>
+      <c r="E83" s="71"/>
+      <c r="F83" s="71"/>
+      <c r="G83" s="71"/>
+      <c r="H83" s="71"/>
+      <c r="I83" s="71"/>
+      <c r="J83" s="71"/>
+      <c r="K83" s="71"/>
+      <c r="L83" s="71"/>
+      <c r="M83" s="71"/>
+      <c r="N83" s="39"/>
       <c r="O83" s="4"/>
       <c r="P83" s="4"/>
       <c r="Q83" s="4"/>
@@ -4934,19 +5493,27 @@
       <c r="U83" s="4"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
+      <c r="A84" s="69" t="s">
+        <v>270</v>
+      </c>
+      <c r="B84" t="s">
+        <v>272</v>
+      </c>
+      <c r="C84" s="69" t="s">
+        <v>273</v>
+      </c>
+      <c r="D84" s="69" t="s">
+        <v>278</v>
+      </c>
+      <c r="E84" s="41"/>
+      <c r="F84" s="41"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="41"/>
+      <c r="I84" s="41"/>
+      <c r="J84" s="41"/>
+      <c r="K84" s="41"/>
+      <c r="L84" s="41"/>
+      <c r="M84" s="41"/>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
       <c r="P84" s="4"/>
@@ -4957,10 +5524,18 @@
       <c r="U84" s="4"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
+      <c r="A85" s="67" t="s">
+        <v>275</v>
+      </c>
+      <c r="B85" s="66">
+        <v>23</v>
+      </c>
+      <c r="C85" s="66">
+        <v>48</v>
+      </c>
+      <c r="D85" s="66">
+        <v>16</v>
+      </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
@@ -4980,10 +5555,18 @@
       <c r="U85" s="4"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
+      <c r="A86" s="67" t="s">
+        <v>276</v>
+      </c>
+      <c r="B86" s="67" t="s">
+        <v>274</v>
+      </c>
+      <c r="C86" s="67" t="s">
+        <v>277</v>
+      </c>
+      <c r="D86" s="66">
+        <v>16</v>
+      </c>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
@@ -5003,10 +5586,18 @@
       <c r="U86" s="4"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
+      <c r="A87" s="50" t="s">
+        <v>279</v>
+      </c>
+      <c r="B87" s="5">
+        <v>23</v>
+      </c>
+      <c r="C87" s="5">
+        <v>48</v>
+      </c>
+      <c r="D87" s="5">
+        <v>16</v>
+      </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
@@ -5026,10 +5617,18 @@
       <c r="U87" s="4"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
+      <c r="A88" s="67" t="s">
+        <v>280</v>
+      </c>
+      <c r="B88" s="66">
+        <v>11</v>
+      </c>
+      <c r="C88" s="66">
+        <v>24</v>
+      </c>
+      <c r="D88" s="66">
+        <v>8</v>
+      </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -5049,10 +5648,18 @@
       <c r="U88" s="4"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
+      <c r="A89" s="67" t="s">
+        <v>281</v>
+      </c>
+      <c r="B89" s="67" t="s">
+        <v>284</v>
+      </c>
+      <c r="C89" s="67" t="s">
+        <v>283</v>
+      </c>
+      <c r="D89" s="66">
+        <v>8</v>
+      </c>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
@@ -5072,10 +5679,18 @@
       <c r="U89" s="4"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
+      <c r="A90" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="B90" s="66">
+        <v>11</v>
+      </c>
+      <c r="C90" s="66">
+        <v>24</v>
+      </c>
+      <c r="D90" s="66">
+        <v>8</v>
+      </c>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
@@ -5095,7 +5710,9 @@
       <c r="U90" s="4"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A91" s="4"/>
+      <c r="A91" s="38" t="s">
+        <v>285</v>
+      </c>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -5141,11 +5758,21 @@
       <c r="U92" s="4"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
+      <c r="A93" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="B93" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="C93" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="D93" s="38" t="s">
+        <v>291</v>
+      </c>
+      <c r="E93" s="38" t="s">
+        <v>292</v>
+      </c>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
@@ -5164,11 +5791,23 @@
       <c r="U93" s="4"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
+      <c r="A94" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="B94" s="38">
+        <f>112*112</f>
+        <v>12544</v>
+      </c>
+      <c r="C94" s="72">
+        <v>16</v>
+      </c>
+      <c r="D94" s="72">
+        <v>4</v>
+      </c>
+      <c r="E94" s="72">
+        <f>B94/C94/D94</f>
+        <v>196</v>
+      </c>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
@@ -5187,11 +5826,23 @@
       <c r="U94" s="4"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
+      <c r="A95" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="B95" s="4">
+        <f>56*56*2</f>
+        <v>6272</v>
+      </c>
+      <c r="C95" s="72">
+        <v>8</v>
+      </c>
+      <c r="D95" s="72">
+        <v>4</v>
+      </c>
+      <c r="E95" s="72">
+        <f>B95/C95/D95</f>
+        <v>196</v>
+      </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
@@ -5233,19 +5884,19 @@
       <c r="U96" s="4"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="4"/>
-      <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
+      <c r="A97" s="40"/>
+      <c r="B97" s="40"/>
+      <c r="C97" s="40"/>
+      <c r="D97" s="40"/>
+      <c r="E97" s="40"/>
+      <c r="F97" s="40"/>
+      <c r="G97" s="40"/>
+      <c r="H97" s="40"/>
+      <c r="I97" s="40"/>
+      <c r="J97" s="40"/>
+      <c r="K97" s="40"/>
+      <c r="L97" s="40"/>
+      <c r="M97" s="40"/>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
       <c r="P97" s="4"/>
@@ -5256,20 +5907,22 @@
       <c r="U97" s="4"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="4"/>
-      <c r="M98" s="4"/>
-      <c r="N98" s="4"/>
+      <c r="A98" s="71" t="s">
+        <v>303</v>
+      </c>
+      <c r="B98" s="71"/>
+      <c r="C98" s="71"/>
+      <c r="D98" s="71"/>
+      <c r="E98" s="71"/>
+      <c r="F98" s="71"/>
+      <c r="G98" s="71"/>
+      <c r="H98" s="71"/>
+      <c r="I98" s="71"/>
+      <c r="J98" s="71"/>
+      <c r="K98" s="71"/>
+      <c r="L98" s="71"/>
+      <c r="M98" s="71"/>
+      <c r="N98" s="39"/>
       <c r="O98" s="4"/>
       <c r="P98" s="4"/>
       <c r="Q98" s="4"/>
@@ -5279,20 +5932,20 @@
       <c r="U98" s="4"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A99" s="4"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
+      <c r="A99" s="71"/>
+      <c r="B99" s="71"/>
+      <c r="C99" s="71"/>
+      <c r="D99" s="71"/>
+      <c r="E99" s="71"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="71"/>
+      <c r="H99" s="71"/>
+      <c r="I99" s="71"/>
+      <c r="J99" s="71"/>
+      <c r="K99" s="71"/>
+      <c r="L99" s="71"/>
+      <c r="M99" s="71"/>
+      <c r="N99" s="39"/>
       <c r="O99" s="4"/>
       <c r="P99" s="4"/>
       <c r="Q99" s="4"/>
@@ -5302,19 +5955,25 @@
       <c r="U99" s="4"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A100" s="4"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
+      <c r="A100" s="69" t="s">
+        <v>294</v>
+      </c>
+      <c r="B100" s="69" t="s">
+        <v>296</v>
+      </c>
+      <c r="C100" s="69" t="s">
+        <v>297</v>
+      </c>
+      <c r="D100" s="41"/>
+      <c r="E100" s="41"/>
+      <c r="F100" s="41"/>
+      <c r="G100" s="41"/>
+      <c r="H100" s="41"/>
+      <c r="I100" s="41"/>
+      <c r="J100" s="41"/>
+      <c r="K100" s="41"/>
+      <c r="L100" s="41"/>
+      <c r="M100" s="41"/>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
       <c r="P100" s="4"/>
@@ -5325,10 +5984,18 @@
       <c r="U100" s="4"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
+      <c r="A101" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="B101" s="73">
+        <v>16</v>
+      </c>
+      <c r="C101" s="73">
+        <v>16</v>
+      </c>
+      <c r="D101" s="38" t="s">
+        <v>299</v>
+      </c>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
@@ -5348,10 +6015,18 @@
       <c r="U101" s="4"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
+      <c r="A102" s="38" t="s">
+        <v>298</v>
+      </c>
+      <c r="B102" s="73">
+        <v>16</v>
+      </c>
+      <c r="C102" s="73">
+        <v>64</v>
+      </c>
+      <c r="D102" s="38" t="s">
+        <v>304</v>
+      </c>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
@@ -5371,9 +6046,15 @@
       <c r="U102" s="4"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
+      <c r="A103" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="B103" s="74" t="s">
+        <v>301</v>
+      </c>
+      <c r="C103" s="74" t="s">
+        <v>301</v>
+      </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
@@ -5394,11 +6075,21 @@
       <c r="U103" s="4"/>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
+      <c r="A104" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="B104" s="73">
+        <v>16</v>
+      </c>
+      <c r="C104" s="73">
+        <v>32</v>
+      </c>
+      <c r="D104" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="E104" s="38" t="s">
+        <v>305</v>
+      </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
@@ -5440,19 +6131,19 @@
       <c r="U105" s="4"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="4"/>
-      <c r="L106" s="4"/>
-      <c r="M106" s="4"/>
+      <c r="A106" s="40"/>
+      <c r="B106" s="40"/>
+      <c r="C106" s="40"/>
+      <c r="D106" s="40"/>
+      <c r="E106" s="40"/>
+      <c r="F106" s="40"/>
+      <c r="G106" s="40"/>
+      <c r="H106" s="40"/>
+      <c r="I106" s="40"/>
+      <c r="J106" s="40"/>
+      <c r="K106" s="40"/>
+      <c r="L106" s="40"/>
+      <c r="M106" s="40"/>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
       <c r="P106" s="4"/>
@@ -5463,20 +6154,22 @@
       <c r="U106" s="4"/>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-      <c r="K107" s="4"/>
-      <c r="L107" s="4"/>
-      <c r="M107" s="4"/>
-      <c r="N107" s="4"/>
+      <c r="A107" s="71" t="s">
+        <v>307</v>
+      </c>
+      <c r="B107" s="70"/>
+      <c r="C107" s="70"/>
+      <c r="D107" s="70"/>
+      <c r="E107" s="70"/>
+      <c r="F107" s="70"/>
+      <c r="G107" s="70"/>
+      <c r="H107" s="70"/>
+      <c r="I107" s="70"/>
+      <c r="J107" s="70"/>
+      <c r="K107" s="70"/>
+      <c r="L107" s="70"/>
+      <c r="M107" s="70"/>
+      <c r="N107" s="39"/>
       <c r="O107" s="4"/>
       <c r="P107" s="4"/>
       <c r="Q107" s="4"/>
@@ -5486,20 +6179,20 @@
       <c r="U107" s="4"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
-      <c r="K108" s="4"/>
-      <c r="L108" s="4"/>
-      <c r="M108" s="4"/>
-      <c r="N108" s="4"/>
+      <c r="A108" s="70"/>
+      <c r="B108" s="70"/>
+      <c r="C108" s="70"/>
+      <c r="D108" s="70"/>
+      <c r="E108" s="70"/>
+      <c r="F108" s="70"/>
+      <c r="G108" s="70"/>
+      <c r="H108" s="70"/>
+      <c r="I108" s="70"/>
+      <c r="J108" s="70"/>
+      <c r="K108" s="70"/>
+      <c r="L108" s="70"/>
+      <c r="M108" s="70"/>
+      <c r="N108" s="39"/>
       <c r="O108" s="4"/>
       <c r="P108" s="4"/>
       <c r="Q108" s="4"/>
@@ -5509,19 +6202,21 @@
       <c r="U108" s="4"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A109" s="4"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-      <c r="E109" s="4"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
-      <c r="K109" s="4"/>
-      <c r="L109" s="4"/>
-      <c r="M109" s="4"/>
+      <c r="A109" s="63" t="s">
+        <v>308</v>
+      </c>
+      <c r="B109" s="75"/>
+      <c r="C109" s="41"/>
+      <c r="D109" s="41"/>
+      <c r="E109" s="41"/>
+      <c r="F109" s="41"/>
+      <c r="G109" s="41"/>
+      <c r="H109" s="41"/>
+      <c r="I109" s="41"/>
+      <c r="J109" s="41"/>
+      <c r="K109" s="41"/>
+      <c r="L109" s="41"/>
+      <c r="M109" s="41"/>
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
       <c r="P109" s="4"/>
@@ -5532,8 +6227,8 @@
       <c r="U109" s="4"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A110" s="4"/>
-      <c r="B110" s="4"/>
+      <c r="A110" s="70"/>
+      <c r="B110" s="39"/>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
@@ -5555,7 +6250,7 @@
       <c r="U110" s="4"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A111" s="4"/>
+      <c r="A111" s="41"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
@@ -7770,10 +8465,14 @@
       <c r="E207" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="30">
+    <mergeCell ref="A98:M99"/>
+    <mergeCell ref="A107:M108"/>
+    <mergeCell ref="A109:A110"/>
     <mergeCell ref="K61:R61"/>
     <mergeCell ref="A61:I61"/>
     <mergeCell ref="P68:R68"/>
+    <mergeCell ref="A82:M83"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="M26:M27"/>
     <mergeCell ref="O25:O26"/>
@@ -7988,11 +8687,11 @@
         <f>C7+$Z$2</f>
         <v>71</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="54">
         <f>D7+$AA$2+18</f>
         <v>81</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="54">
         <f>E7+$AB$2</f>
         <v>97</v>
       </c>
@@ -8048,20 +8747,20 @@
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
     </row>
     <row r="19" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19"/>
@@ -8248,11 +8947,11 @@
         <f>C6+$Z$2</f>
         <v>273</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="54">
         <f>D6+$AA$2+18</f>
         <v>283</v>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="54">
         <f>E6+$AB$2</f>
         <v>299</v>
       </c>
@@ -8273,11 +8972,11 @@
         <f>C7+$Q$2</f>
         <v>351</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="53">
         <f>D7+$R$2+75</f>
         <v>402</v>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="53">
         <f>E7+64</f>
         <v>466</v>
       </c>
@@ -8298,11 +8997,11 @@
         <f>C8+$Q$2</f>
         <v>429</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="54">
         <f>D8+$R$2+61</f>
         <v>466</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="54">
         <f>E8+$S$2</f>
         <v>530</v>
       </c>
@@ -8348,11 +9047,11 @@
         <f>C10+$Z$2</f>
         <v>475</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="54">
         <f>D10+$AA$2+18</f>
         <v>485</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="54">
         <f>E10+$AB$2</f>
         <v>501</v>
       </c>
@@ -8361,7 +9060,7 @@
       <c r="A11" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="51">
+      <c r="B11" s="54">
         <f>D10-1</f>
         <v>474</v>
       </c>
@@ -8373,11 +9072,11 @@
         <f>C11+$Q$2</f>
         <v>554</v>
       </c>
-      <c r="E11" s="53">
+      <c r="E11" s="56">
         <f>D11+$R$2</f>
         <v>530</v>
       </c>
-      <c r="F11" s="53">
+      <c r="F11" s="56">
         <f>E11+$S$2</f>
         <v>594</v>
       </c>
@@ -8398,11 +9097,11 @@
         <f>C12+$Q$2</f>
         <v>632</v>
       </c>
-      <c r="E12" s="53">
+      <c r="E12" s="56">
         <f>D12+$R$2</f>
         <v>608</v>
       </c>
-      <c r="F12" s="53">
+      <c r="F12" s="56">
         <f>E12+$S$2</f>
         <v>672</v>
       </c>
@@ -8448,11 +9147,11 @@
         <f>C14+$Z$2</f>
         <v>678</v>
       </c>
-      <c r="E14" s="52">
+      <c r="E14" s="55">
         <f>D14+$AA$2</f>
         <v>670</v>
       </c>
-      <c r="F14" s="52">
+      <c r="F14" s="55">
         <f>E14+$AB$2</f>
         <v>686</v>
       </c>
@@ -8940,24 +9639,24 @@
         <v>141</v>
       </c>
       <c r="B16">
-        <f>D28-2</f>
-        <v>110</v>
+        <f>F15</f>
+        <v>112</v>
       </c>
       <c r="C16">
         <f>B16+$P$2</f>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D16">
         <f>C16+$Q$2</f>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E16">
         <f>D16+$R$2</f>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F16">
         <f>E16+$S$2</f>
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -8966,19 +9665,19 @@
       </c>
       <c r="C17">
         <f>E16</f>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D17">
         <f>C17+$U$2</f>
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E17">
         <f>D17+$V$2</f>
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F17">
         <f>E17+$W$2</f>
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -8987,19 +9686,19 @@
       </c>
       <c r="C18">
         <f>F17</f>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D18">
         <f>C18+$H$2</f>
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E18">
         <f>D18+$I$2</f>
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F18">
         <f>E18+$J$2</f>
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -9008,19 +9707,19 @@
       </c>
       <c r="C19">
         <f>F18</f>
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D19">
         <f>C19+$L$2</f>
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E19">
         <f>D19+$M$2</f>
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F19">
         <f>E19+$N$2</f>
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -9028,24 +9727,24 @@
         <v>142</v>
       </c>
       <c r="B20">
-        <f>D34-2</f>
-        <v>142</v>
+        <f>F19</f>
+        <v>146</v>
       </c>
       <c r="C20">
         <f>B20+$P$2</f>
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D20">
         <f>C20+$Q$2</f>
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E20">
         <f>D20+$R$2</f>
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F20">
         <f>E20+$S$2</f>
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -9054,19 +9753,19 @@
       </c>
       <c r="C21">
         <f>E20</f>
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D21">
         <f>C21+$U$2</f>
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E21">
         <f>D21+$V$2</f>
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F21">
         <f>E21+$W$2</f>
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -9075,19 +9774,19 @@
       </c>
       <c r="C22">
         <f>F21</f>
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D22">
         <f>C22+$H$2</f>
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E22">
         <f>D22+$I$2</f>
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F22">
         <f>E22+$J$2</f>
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -9096,19 +9795,19 @@
       </c>
       <c r="C23">
         <f>F22</f>
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D23">
         <f>C23+$L$2</f>
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E23">
         <f>D23+$M$2</f>
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F23">
         <f>E23+$N$2</f>
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -9117,15 +9816,15 @@
       </c>
       <c r="D24">
         <f>F23</f>
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E24">
         <f>D24+7</f>
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F24">
         <f>E24+1</f>
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -9309,23 +10008,23 @@
       </c>
       <c r="B32">
         <f>D16-2</f>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C32">
         <f>B32+$P$2</f>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D32">
         <f>C32+$Q$2</f>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E32">
         <f>D32+$R$2</f>
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F32">
         <f>E32+$S$2</f>
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -9334,23 +10033,23 @@
       </c>
       <c r="B33">
         <f>B32+8</f>
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C33">
         <f>B33+$P$2</f>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D33">
         <f>C33+$Q$2</f>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E33">
         <f>D33+$R$2</f>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F33">
         <f>E33+$S$2</f>
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -9359,23 +10058,23 @@
       </c>
       <c r="B34">
         <f>D33-2</f>
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C34">
         <f>B34+$P$2</f>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D34">
         <f>C34+$Q$2</f>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E34">
         <f>D34+$R$2</f>
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F34">
         <f>E34+$S$2</f>
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -9929,11 +10628,11 @@
         <f>C20+$Q$2</f>
         <v>340</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="54">
         <f>D20+$R$2+1</f>
         <v>343</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="54">
         <f>E20+$S$2</f>
         <v>345</v>
       </c>
@@ -10234,11 +10933,11 @@
         <f>C33+$Q$2</f>
         <v>322</v>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="54">
         <f>D33+$R$2+1</f>
         <v>325</v>
       </c>
-      <c r="F33" s="51">
+      <c r="F33" s="54">
         <f>E33+$S$2</f>
         <v>327</v>
       </c>
@@ -10259,11 +10958,11 @@
         <f>C34+$Q$2</f>
         <v>330</v>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="54">
         <f>D34+$R$2+1</f>
         <v>333</v>
       </c>
-      <c r="F34" s="51">
+      <c r="F34" s="54">
         <f>E34+$S$2</f>
         <v>335</v>
       </c>
@@ -10562,11 +11261,11 @@
         <f>C7+$Q$6</f>
         <v>68</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="53">
         <f>D7+$R$6+58</f>
         <v>126</v>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="53">
         <f>E7+$S$6</f>
         <v>134</v>
       </c>
@@ -10622,20 +11321,20 @@
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
     </row>
     <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18"/>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="1"/>
@@ -10946,11 +11645,11 @@
         <f>C7+$Q$6</f>
         <v>252</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="54">
         <f>D7+$R$6+34</f>
         <v>286</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="54">
         <f>E7+$S$6</f>
         <v>294</v>
       </c>
@@ -10971,11 +11670,11 @@
         <f>C8+$Q$4</f>
         <v>296</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="54">
         <f>D8+$R$4+44+61</f>
         <v>365</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="54">
         <f>E8+32</f>
         <v>397</v>
       </c>
@@ -10984,7 +11683,7 @@
       <c r="A9" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="51">
+      <c r="B9" s="54">
         <f>D8-2+17</f>
         <v>311</v>
       </c>
@@ -11095,13 +11794,13 @@
         <f>C13+$Q$4</f>
         <v>512</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="54">
         <f>D13+$R$4+45</f>
         <v>521</v>
       </c>
-      <c r="F13" s="51">
-        <f>E13+16</f>
-        <v>537</v>
+      <c r="F13" s="54">
+        <f>E13+32</f>
+        <v>553</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
@@ -11120,13 +11819,13 @@
         <f>C14+$Q$4</f>
         <v>556</v>
       </c>
-      <c r="E14" s="51">
-        <f>D14+$R$4+25</f>
-        <v>545</v>
-      </c>
-      <c r="F14" s="51">
-        <f>E14+16</f>
-        <v>561</v>
+      <c r="E14" s="54">
+        <f>D14+$R$4+35</f>
+        <v>555</v>
+      </c>
+      <c r="F14" s="54">
+        <f>E14+32</f>
+        <v>587</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
@@ -11218,895 +11917,1092 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A37FD03-BF78-46BE-832D-3A5B174965E9}">
-  <dimension ref="A1:AB34"/>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374C6790-0C84-44DF-9CE1-7C181D6C9B9E}">
+  <dimension ref="A1:BB42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="3" max="59" width="4.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>163</v>
-      </c>
-      <c r="H1" t="str">
-        <f>v0!A62</f>
-        <v>inter pk in</v>
-      </c>
-      <c r="I1" t="str">
-        <f>v0!B62</f>
-        <v>inter pk work</v>
-      </c>
-      <c r="J1" t="str">
-        <f>v0!C62</f>
-        <v>inter pk out</v>
-      </c>
-      <c r="L1" t="str">
-        <f>v0!A64</f>
-        <v>sel pk in</v>
-      </c>
-      <c r="M1" t="str">
-        <f>v0!B64</f>
-        <v>sel pk work</v>
-      </c>
-      <c r="N1" t="str">
-        <f>v0!C64</f>
-        <v>sel pk out</v>
-      </c>
-      <c r="P1" t="str">
-        <f>v0!A70</f>
-        <v>Yread latancy</v>
-      </c>
-      <c r="Q1" t="str">
-        <f>v0!B70</f>
-        <v>8x8 input cc</v>
-      </c>
-      <c r="R1" t="str">
-        <f>v0!C70</f>
-        <v>8x8 work cc</v>
-      </c>
-      <c r="S1" t="str">
-        <f>v0!D70</f>
-        <v>8x8 output cc</v>
-      </c>
-      <c r="U1" t="str">
-        <f>v0!G62</f>
-        <v>tqitq8x8 input</v>
-      </c>
-      <c r="V1" t="str">
-        <f>v0!H62</f>
-        <v>tqitq work</v>
-      </c>
-      <c r="W1" t="str">
-        <f>v0!I62</f>
-        <v>tqitq out</v>
-      </c>
-      <c r="Y1" t="str">
-        <f>v0!A68</f>
-        <v>Yread latancy</v>
-      </c>
-      <c r="Z1" t="str">
-        <f>v0!B68</f>
-        <v>16x16 input cc</v>
-      </c>
-      <c r="AA1" t="str">
-        <f>v0!C68</f>
-        <v>16x16 work cc</v>
-      </c>
-      <c r="AB1" t="str">
-        <f>v0!D68</f>
-        <v>16x16 output cc</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="87" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="88"/>
+      <c r="Z1" s="89"/>
+      <c r="AC1" s="87" t="s">
+        <v>323</v>
+      </c>
+      <c r="AD1" s="88"/>
+      <c r="AE1" s="88"/>
+      <c r="AF1" s="88"/>
+      <c r="AG1" s="88"/>
+      <c r="AH1" s="88"/>
+      <c r="AI1" s="88"/>
+      <c r="AJ1" s="88"/>
+      <c r="AK1" s="88"/>
+      <c r="AL1" s="88"/>
+      <c r="AM1" s="88"/>
+      <c r="AN1" s="88"/>
+      <c r="AO1" s="88"/>
+      <c r="AP1" s="88"/>
+      <c r="AQ1" s="88"/>
+      <c r="AR1" s="88"/>
+      <c r="AS1" s="88"/>
+      <c r="AT1" s="88"/>
+      <c r="AU1" s="88"/>
+      <c r="AV1" s="89"/>
+    </row>
+    <row r="2" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H2" t="s">
+        <v>322</v>
+      </c>
+      <c r="O2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>314</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>324</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>325</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" s="81" t="s">
+        <v>312</v>
+      </c>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="83"/>
+      <c r="H3" s="81" t="s">
+        <v>313</v>
+      </c>
+      <c r="I3" s="83"/>
+      <c r="J3" s="81">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="K3" s="83"/>
+      <c r="O3" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q3" s="87" t="s">
+        <v>328</v>
+      </c>
+      <c r="R3" s="89"/>
+      <c r="AC3" t="s">
+        <v>309</v>
+      </c>
+      <c r="AE3" s="81" t="s">
+        <v>312</v>
+      </c>
+      <c r="AF3" s="82"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="83"/>
+      <c r="AJ3" s="81" t="s">
+        <v>313</v>
+      </c>
+      <c r="AK3" s="83"/>
+      <c r="AL3" s="81">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="83"/>
+      <c r="AX3" t="s">
+        <v>309</v>
+      </c>
+      <c r="AY3" s="81" t="s">
+        <v>313</v>
+      </c>
+      <c r="AZ3" s="83"/>
+      <c r="BA3" s="81">
+        <v>1</v>
+      </c>
+      <c r="BB3" s="83"/>
+    </row>
+    <row r="4" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="84"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="86"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="93"/>
+      <c r="Q4" s="90"/>
+      <c r="R4" s="91"/>
+      <c r="AE4" s="84"/>
+      <c r="AF4" s="85"/>
+      <c r="AG4" s="85"/>
+      <c r="AH4" s="86"/>
+      <c r="AJ4" s="92"/>
+      <c r="AK4" s="93"/>
+      <c r="AL4" s="92"/>
+      <c r="AM4" s="93"/>
+      <c r="AY4" s="92"/>
+      <c r="AZ4" s="93"/>
+      <c r="BA4" s="92"/>
+      <c r="BB4" s="93"/>
+    </row>
+    <row r="5" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="81">
+        <v>1</v>
+      </c>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="83"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="93"/>
+      <c r="AE5" s="81">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="82"/>
+      <c r="AG5" s="82"/>
+      <c r="AH5" s="83"/>
+      <c r="AJ5" s="92"/>
+      <c r="AK5" s="93"/>
+      <c r="AL5" s="92"/>
+      <c r="AM5" s="93"/>
+      <c r="AY5" s="92"/>
+      <c r="AZ5" s="93"/>
+      <c r="BA5" s="92"/>
+      <c r="BB5" s="93"/>
+    </row>
+    <row r="6" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="84"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="86"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="86"/>
+      <c r="Q6" s="81" t="s">
+        <v>329</v>
+      </c>
+      <c r="R6" s="83"/>
+      <c r="AE6" s="84"/>
+      <c r="AF6" s="85"/>
+      <c r="AG6" s="85"/>
+      <c r="AH6" s="86"/>
+      <c r="AJ6" s="84"/>
+      <c r="AK6" s="86"/>
+      <c r="AL6" s="84"/>
+      <c r="AM6" s="86"/>
+      <c r="AY6" s="84"/>
+      <c r="AZ6" s="86"/>
+      <c r="BA6" s="84"/>
+      <c r="BB6" s="86"/>
+    </row>
+    <row r="7" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="81">
         <v>2</v>
       </c>
-      <c r="H2">
-        <f>v0!A63</f>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="83"/>
+      <c r="H7" s="81">
+        <v>2</v>
+      </c>
+      <c r="I7" s="83"/>
+      <c r="J7" s="81">
+        <v>3</v>
+      </c>
+      <c r="K7" s="83"/>
+      <c r="Q7" s="90"/>
+      <c r="R7" s="91"/>
+      <c r="AE7" s="81">
+        <v>2</v>
+      </c>
+      <c r="AF7" s="82"/>
+      <c r="AG7" s="82"/>
+      <c r="AH7" s="83"/>
+      <c r="AJ7" s="81">
+        <v>2</v>
+      </c>
+      <c r="AK7" s="83"/>
+      <c r="AL7" s="81">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="83"/>
+      <c r="AY7" s="81">
+        <v>2</v>
+      </c>
+      <c r="AZ7" s="83"/>
+      <c r="BA7" s="81">
+        <v>3</v>
+      </c>
+      <c r="BB7" s="83"/>
+    </row>
+    <row r="8" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="84"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="86"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="93"/>
+      <c r="AE8" s="84"/>
+      <c r="AF8" s="85"/>
+      <c r="AG8" s="85"/>
+      <c r="AH8" s="86"/>
+      <c r="AJ8" s="92"/>
+      <c r="AK8" s="93"/>
+      <c r="AL8" s="92"/>
+      <c r="AM8" s="93"/>
+      <c r="AY8" s="92"/>
+      <c r="AZ8" s="93"/>
+      <c r="BA8" s="92"/>
+      <c r="BB8" s="93"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="C9" s="76"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="77"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="93"/>
+      <c r="AE9" s="76"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="77"/>
+      <c r="AJ9" s="92"/>
+      <c r="AK9" s="93"/>
+      <c r="AL9" s="92"/>
+      <c r="AM9" s="93"/>
+      <c r="AY9" s="92"/>
+      <c r="AZ9" s="93"/>
+      <c r="BA9" s="92"/>
+      <c r="BB9" s="93"/>
+    </row>
+    <row r="10" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="78"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="80"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="86"/>
+      <c r="AE10" s="78"/>
+      <c r="AF10" s="79"/>
+      <c r="AG10" s="79"/>
+      <c r="AH10" s="80"/>
+      <c r="AJ10" s="84"/>
+      <c r="AK10" s="86"/>
+      <c r="AL10" s="84"/>
+      <c r="AM10" s="86"/>
+      <c r="AY10" s="84"/>
+      <c r="AZ10" s="86"/>
+      <c r="BA10" s="84"/>
+      <c r="BB10" s="86"/>
+    </row>
+    <row r="12" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>310</v>
+      </c>
+      <c r="C13" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="89"/>
+      <c r="O13" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q13" s="87" t="s">
+        <v>326</v>
+      </c>
+      <c r="R13" s="88"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="89"/>
+      <c r="V13" s="87" t="s">
+        <v>327</v>
+      </c>
+      <c r="W13" s="88"/>
+      <c r="X13" s="88"/>
+      <c r="Y13" s="89"/>
+      <c r="AC13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AE13" s="85" t="s">
+        <v>330</v>
+      </c>
+      <c r="AF13" s="85"/>
+      <c r="AG13" s="85"/>
+      <c r="AH13" s="85"/>
+      <c r="AN13" s="85" t="s">
+        <v>322</v>
+      </c>
+      <c r="AO13" s="85"/>
+      <c r="AP13" s="85"/>
+      <c r="AQ13" s="85"/>
+    </row>
+    <row r="14" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="81">
         <v>1</v>
       </c>
-      <c r="I2">
-        <f>v0!B63</f>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="83"/>
+      <c r="Q14" s="87">
         <v>1</v>
       </c>
-      <c r="J2">
-        <f>v0!C63</f>
+      <c r="R14" s="88"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="89"/>
+      <c r="V14" s="87">
         <v>1</v>
       </c>
-      <c r="L2">
-        <f>v0!A65</f>
+      <c r="W14" s="88"/>
+      <c r="X14" s="88"/>
+      <c r="Y14" s="89"/>
+      <c r="AE14" s="81" t="s">
+        <v>312</v>
+      </c>
+      <c r="AF14" s="82"/>
+      <c r="AG14" s="82"/>
+      <c r="AH14" s="83"/>
+      <c r="AI14" s="81" t="s">
+        <v>331</v>
+      </c>
+      <c r="AJ14" s="82"/>
+      <c r="AK14" s="82"/>
+      <c r="AL14" s="83"/>
+      <c r="AN14" s="81">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="83"/>
+      <c r="AP14" s="81">
         <v>1</v>
       </c>
-      <c r="M2">
-        <f>v0!B65</f>
+      <c r="AQ14" s="83"/>
+      <c r="AR14" s="81">
+        <v>8</v>
+      </c>
+      <c r="AS14" s="83"/>
+      <c r="AT14" s="81">
+        <v>9</v>
+      </c>
+      <c r="AU14" s="83"/>
+    </row>
+    <row r="15" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="76"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="77"/>
+      <c r="Q15" s="87">
+        <v>2</v>
+      </c>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="89"/>
+      <c r="V15" s="87">
+        <v>2</v>
+      </c>
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+      <c r="Y15" s="89"/>
+      <c r="AE15" s="84"/>
+      <c r="AF15" s="85"/>
+      <c r="AG15" s="85"/>
+      <c r="AH15" s="86"/>
+      <c r="AI15" s="84"/>
+      <c r="AJ15" s="85"/>
+      <c r="AK15" s="85"/>
+      <c r="AL15" s="86"/>
+      <c r="AN15" s="84"/>
+      <c r="AO15" s="86"/>
+      <c r="AP15" s="84"/>
+      <c r="AQ15" s="86"/>
+      <c r="AR15" s="84"/>
+      <c r="AS15" s="86"/>
+      <c r="AT15" s="84"/>
+      <c r="AU15" s="86"/>
+    </row>
+    <row r="16" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="76"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="77"/>
+      <c r="Q16" s="87">
+        <v>3</v>
+      </c>
+      <c r="R16" s="88"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="89"/>
+      <c r="V16" s="87">
+        <v>3</v>
+      </c>
+      <c r="W16" s="88"/>
+      <c r="X16" s="88"/>
+      <c r="Y16" s="89"/>
+      <c r="AE16" s="81">
         <v>1</v>
       </c>
-      <c r="N2">
-        <f>v0!C65</f>
+      <c r="AF16" s="82"/>
+      <c r="AG16" s="82"/>
+      <c r="AH16" s="83"/>
+      <c r="AI16" s="81">
+        <v>9</v>
+      </c>
+      <c r="AJ16" s="82"/>
+      <c r="AK16" s="82"/>
+      <c r="AL16" s="83"/>
+      <c r="AN16" s="81">
+        <v>2</v>
+      </c>
+      <c r="AO16" s="83"/>
+      <c r="AP16" s="81">
+        <v>3</v>
+      </c>
+      <c r="AQ16" s="83"/>
+      <c r="AR16" s="81">
+        <v>10</v>
+      </c>
+      <c r="AS16" s="83"/>
+      <c r="AT16" s="81">
+        <v>11</v>
+      </c>
+      <c r="AU16" s="83"/>
+    </row>
+    <row r="17" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="76"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="77"/>
+      <c r="Q17" s="76"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="77"/>
+      <c r="V17" s="76"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="77"/>
+      <c r="AE17" s="84"/>
+      <c r="AF17" s="85"/>
+      <c r="AG17" s="85"/>
+      <c r="AH17" s="86"/>
+      <c r="AI17" s="84"/>
+      <c r="AJ17" s="85"/>
+      <c r="AK17" s="85"/>
+      <c r="AL17" s="86"/>
+      <c r="AN17" s="84"/>
+      <c r="AO17" s="86"/>
+      <c r="AP17" s="84"/>
+      <c r="AQ17" s="86"/>
+      <c r="AR17" s="84"/>
+      <c r="AS17" s="86"/>
+      <c r="AT17" s="84"/>
+      <c r="AU17" s="86"/>
+    </row>
+    <row r="18" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="C18" s="76"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="77"/>
+      <c r="Q18" s="76"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="77"/>
+      <c r="V18" s="76"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="77"/>
+      <c r="AE18" s="81"/>
+      <c r="AF18" s="82"/>
+      <c r="AG18" s="82"/>
+      <c r="AH18" s="83"/>
+      <c r="AI18" s="81"/>
+      <c r="AJ18" s="82"/>
+      <c r="AK18" s="82"/>
+      <c r="AL18" s="83"/>
+      <c r="AN18" s="81">
+        <v>4</v>
+      </c>
+      <c r="AO18" s="83"/>
+      <c r="AP18" s="81">
+        <v>5</v>
+      </c>
+      <c r="AQ18" s="83"/>
+      <c r="AR18" s="81">
+        <v>12</v>
+      </c>
+      <c r="AS18" s="83"/>
+      <c r="AT18" s="81">
+        <v>13</v>
+      </c>
+      <c r="AU18" s="83"/>
+    </row>
+    <row r="19" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="76"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="77"/>
+      <c r="Q19" s="76"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="77"/>
+      <c r="V19" s="76"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="77"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="85"/>
+      <c r="AG19" s="85"/>
+      <c r="AH19" s="86"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
+      <c r="AK19" s="85"/>
+      <c r="AL19" s="86"/>
+      <c r="AN19" s="84"/>
+      <c r="AO19" s="86"/>
+      <c r="AP19" s="84"/>
+      <c r="AQ19" s="86"/>
+      <c r="AR19" s="84"/>
+      <c r="AS19" s="86"/>
+      <c r="AT19" s="84"/>
+      <c r="AU19" s="86"/>
+    </row>
+    <row r="20" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="87">
+        <v>15</v>
+      </c>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="89"/>
+      <c r="Q20" s="87">
+        <v>15</v>
+      </c>
+      <c r="R20" s="88"/>
+      <c r="S20" s="88"/>
+      <c r="T20" s="89"/>
+      <c r="V20" s="87">
+        <v>15</v>
+      </c>
+      <c r="W20" s="88"/>
+      <c r="X20" s="88"/>
+      <c r="Y20" s="89"/>
+      <c r="AE20" s="81">
+        <v>7</v>
+      </c>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="81">
+        <v>15</v>
+      </c>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="83"/>
+      <c r="AN20" s="81">
+        <v>6</v>
+      </c>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="81">
+        <v>7</v>
+      </c>
+      <c r="AQ20" s="83"/>
+      <c r="AR20" s="81">
+        <v>14</v>
+      </c>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="81">
+        <v>15</v>
+      </c>
+      <c r="AU20" s="83"/>
+    </row>
+    <row r="21" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AE21" s="84"/>
+      <c r="AF21" s="85"/>
+      <c r="AG21" s="85"/>
+      <c r="AH21" s="86"/>
+      <c r="AI21" s="84"/>
+      <c r="AJ21" s="85"/>
+      <c r="AK21" s="85"/>
+      <c r="AL21" s="86"/>
+      <c r="AN21" s="84"/>
+      <c r="AO21" s="86"/>
+      <c r="AP21" s="84"/>
+      <c r="AQ21" s="86"/>
+      <c r="AR21" s="84"/>
+      <c r="AS21" s="86"/>
+      <c r="AT21" s="84"/>
+      <c r="AU21" s="86"/>
+    </row>
+    <row r="22" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>315</v>
+      </c>
+      <c r="C22" t="s">
+        <v>333</v>
+      </c>
+      <c r="O22" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="87" t="s">
+        <v>317</v>
+      </c>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
+      <c r="Q23" s="87" t="s">
+        <v>320</v>
+      </c>
+      <c r="R23" s="88"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="89"/>
+      <c r="U23" s="87" t="s">
+        <v>321</v>
+      </c>
+      <c r="V23" s="88"/>
+      <c r="W23" s="88"/>
+      <c r="X23" s="89"/>
+    </row>
+    <row r="24" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="87">
         <v>1</v>
       </c>
-      <c r="P2">
-        <f>v0!A71</f>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="77"/>
+      <c r="Q24" s="87">
+        <v>1</v>
+      </c>
+      <c r="R24" s="88"/>
+      <c r="S24" s="88"/>
+      <c r="T24" s="89"/>
+      <c r="U24" s="76"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="77"/>
+    </row>
+    <row r="25" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="87">
         <v>2</v>
       </c>
-      <c r="Q2">
-        <f>v0!B71</f>
-        <v>8</v>
-      </c>
-      <c r="R2">
-        <f>v0!C71</f>
-        <v>4</v>
-      </c>
-      <c r="S2">
-        <f>v0!D71</f>
-        <v>4</v>
-      </c>
-      <c r="U2">
-        <f>v0!G63</f>
-        <v>4</v>
-      </c>
-      <c r="V2">
-        <f>v0!H63</f>
-        <v>23</v>
-      </c>
-      <c r="W2">
-        <f>v0!I63</f>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="77"/>
+      <c r="Q25" s="87">
+        <v>2</v>
+      </c>
+      <c r="R25" s="88"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="89"/>
+      <c r="U25" s="76"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="77"/>
+    </row>
+    <row r="26" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="87">
+        <v>3</v>
+      </c>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="77"/>
+      <c r="Q26" s="87">
+        <v>3</v>
+      </c>
+      <c r="R26" s="88"/>
+      <c r="S26" s="88"/>
+      <c r="T26" s="89"/>
+      <c r="U26" s="76"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="77"/>
+    </row>
+    <row r="27" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="C27" s="76"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="77"/>
+      <c r="Q27" s="76"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="77"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="77"/>
+    </row>
+    <row r="28" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="C28" s="76"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="77"/>
+      <c r="Q28" s="76"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="77"/>
+      <c r="U28" s="76"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="77"/>
+    </row>
+    <row r="29" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="76"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="77"/>
+      <c r="Q29" s="76"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="77"/>
+      <c r="U29" s="76"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="77"/>
+    </row>
+    <row r="30" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="87">
+        <v>31</v>
+      </c>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="84">
+        <v>63</v>
+      </c>
+      <c r="H30" s="85"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="86"/>
+      <c r="Q30" s="87">
+        <v>15</v>
+      </c>
+      <c r="R30" s="88"/>
+      <c r="S30" s="88"/>
+      <c r="T30" s="89"/>
+      <c r="U30" s="84">
+        <v>31</v>
+      </c>
+      <c r="V30" s="85"/>
+      <c r="W30" s="85"/>
+      <c r="X30" s="86"/>
+    </row>
+    <row r="32" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="94" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q32" s="94" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="H33" s="88"/>
+      <c r="I33" s="88"/>
+      <c r="J33" s="89"/>
+      <c r="Q33" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="R33" s="88"/>
+      <c r="S33" s="88"/>
+      <c r="T33" s="89"/>
+    </row>
+    <row r="34" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="87">
+        <v>2</v>
+      </c>
+      <c r="D34" s="88"/>
+      <c r="E34" s="88"/>
+      <c r="F34" s="89"/>
+      <c r="G34" s="87">
+        <v>3</v>
+      </c>
+      <c r="H34" s="88"/>
+      <c r="I34" s="88"/>
+      <c r="J34" s="89"/>
+      <c r="Q34" s="81">
         <v>1</v>
       </c>
-      <c r="Y2">
-        <f>v0!A69</f>
-        <v>2</v>
-      </c>
-      <c r="Z2">
-        <f>v0!B69</f>
-        <v>23</v>
-      </c>
-      <c r="AA2">
-        <f>v0!C69</f>
-        <v>-8</v>
-      </c>
-      <c r="AB2">
-        <f>v0!D69</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <f>B5+$P$2</f>
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <f>C5+$Q$2</f>
-        <v>10</v>
-      </c>
-      <c r="E5">
-        <f>D5+$R$2</f>
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <f>E5+$S$2</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6">
-        <f>B5+8</f>
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <f t="shared" ref="C6:C8" si="0">B6+$P$2</f>
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <f t="shared" ref="D6:D8" si="1">C6+$Q$2</f>
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <f t="shared" ref="E6:E8" si="2">D6+$R$2</f>
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <f t="shared" ref="F6:F8" si="3">E6+$S$2</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7">
-        <f>B6+8</f>
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8">
-        <f>B7+8</f>
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="2"/>
-        <v>38</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="3"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9">
-        <f>E8</f>
-        <v>38</v>
-      </c>
-      <c r="D9">
-        <f>C9+$U$2</f>
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <f>D9+$V$2</f>
-        <v>65</v>
-      </c>
-      <c r="F9">
-        <f>E9+$W$2</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10">
-        <f>F9</f>
-        <v>66</v>
-      </c>
-      <c r="D10">
-        <f>C10+$H$2</f>
-        <v>67</v>
-      </c>
-      <c r="E10">
-        <f>D10+$I$2</f>
-        <v>68</v>
-      </c>
-      <c r="F10">
-        <f>E10+$J$2</f>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11">
-        <f>F10</f>
-        <v>69</v>
-      </c>
-      <c r="D11">
-        <f>C11+$L$2</f>
-        <v>70</v>
-      </c>
-      <c r="E11">
-        <f>D11+$M$2</f>
-        <v>71</v>
-      </c>
-      <c r="F11">
-        <f>E11+$N$2</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12">
-        <f>D31-2</f>
-        <v>79</v>
-      </c>
-      <c r="C12">
-        <f>B12+$P$2</f>
-        <v>81</v>
-      </c>
-      <c r="D12">
-        <f>C12+$Q$2</f>
-        <v>89</v>
-      </c>
-      <c r="E12">
-        <f>D12+$R$2</f>
-        <v>93</v>
-      </c>
-      <c r="F12">
-        <f>E12+$S$2</f>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13">
-        <f>E12</f>
-        <v>93</v>
-      </c>
-      <c r="D13">
-        <f>C13+$U$2</f>
-        <v>97</v>
-      </c>
-      <c r="E13">
-        <f>D13+$V$2</f>
-        <v>120</v>
-      </c>
-      <c r="F13">
-        <f>E13+$W$2</f>
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14">
-        <f>F13</f>
-        <v>121</v>
-      </c>
-      <c r="D14">
-        <f>C14+$H$2</f>
-        <v>122</v>
-      </c>
-      <c r="E14">
-        <f>D14+$I$2</f>
-        <v>123</v>
-      </c>
-      <c r="F14">
-        <f>E14+$J$2</f>
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15">
-        <f>F14</f>
-        <v>124</v>
-      </c>
-      <c r="D15">
-        <f>C15+$L$2</f>
-        <v>125</v>
-      </c>
-      <c r="E15">
-        <f>D15+$M$2</f>
-        <v>126</v>
-      </c>
-      <c r="F15">
-        <f>E15+$N$2</f>
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16">
-        <f>F15</f>
-        <v>127</v>
-      </c>
-      <c r="C16">
-        <f>B16+$P$2</f>
-        <v>129</v>
-      </c>
-      <c r="D16">
-        <f>C16+$Q$2</f>
-        <v>137</v>
-      </c>
-      <c r="E16">
-        <f>D16+$R$2</f>
-        <v>141</v>
-      </c>
-      <c r="F16">
-        <f>E16+$S$2</f>
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17">
-        <f>E16</f>
-        <v>141</v>
-      </c>
-      <c r="D17">
-        <f>C17+$U$2</f>
-        <v>145</v>
-      </c>
-      <c r="E17">
-        <f>D17+$V$2</f>
-        <v>168</v>
-      </c>
-      <c r="F17">
-        <f>E17+$W$2</f>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18">
-        <f>F17</f>
-        <v>169</v>
-      </c>
-      <c r="D18">
-        <f>C18+$H$2</f>
-        <v>170</v>
-      </c>
-      <c r="E18">
-        <f>D18+$I$2</f>
-        <v>171</v>
-      </c>
-      <c r="F18">
-        <f>E18+$J$2</f>
-        <v>172</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19">
-        <f>F18</f>
-        <v>172</v>
-      </c>
-      <c r="D19">
-        <f>C19+$L$2</f>
-        <v>173</v>
-      </c>
-      <c r="E19">
-        <f>D19+$M$2</f>
-        <v>174</v>
-      </c>
-      <c r="F19">
-        <f>E19+$N$2</f>
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20">
-        <f>F19</f>
-        <v>175</v>
-      </c>
-      <c r="C20">
-        <f>B20+$P$2</f>
-        <v>177</v>
-      </c>
-      <c r="D20">
-        <f>C20+$Q$2</f>
-        <v>185</v>
-      </c>
-      <c r="E20">
-        <f>D20+$R$2</f>
-        <v>189</v>
-      </c>
-      <c r="F20">
-        <f>E20+$S$2</f>
-        <v>193</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21">
-        <f>E20</f>
-        <v>189</v>
-      </c>
-      <c r="D21">
-        <f>C21+$U$2</f>
-        <v>193</v>
-      </c>
-      <c r="E21">
-        <f>D21+$V$2</f>
-        <v>216</v>
-      </c>
-      <c r="F21">
-        <f>E21+$W$2</f>
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22">
-        <f>F21</f>
-        <v>217</v>
-      </c>
-      <c r="D22">
-        <f>C22+$H$2</f>
-        <v>218</v>
-      </c>
-      <c r="E22">
-        <f>D22+$I$2</f>
-        <v>219</v>
-      </c>
-      <c r="F22">
-        <f>E22+$J$2</f>
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23">
-        <f>F22</f>
-        <v>220</v>
-      </c>
-      <c r="D23">
-        <f>C23+$L$2</f>
-        <v>221</v>
-      </c>
-      <c r="E23">
-        <f>D23+$M$2</f>
-        <v>222</v>
-      </c>
-      <c r="F23">
-        <f>E23+$N$2</f>
-        <v>223</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24">
-        <f>F23</f>
-        <v>223</v>
-      </c>
-      <c r="E24">
-        <f>D24+7</f>
-        <v>230</v>
-      </c>
-      <c r="F24">
-        <f>E24+1</f>
-        <v>231</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25">
-        <f>B8+8</f>
-        <v>32</v>
-      </c>
-      <c r="C25">
-        <f t="shared" ref="C25:C26" si="4">B25+$P$2</f>
-        <v>34</v>
-      </c>
-      <c r="D25">
-        <f t="shared" ref="D25:D26" si="5">C25+$Q$2</f>
-        <v>42</v>
-      </c>
-      <c r="E25">
-        <f t="shared" ref="E25:E26" si="6">D25+$R$2</f>
-        <v>46</v>
-      </c>
-      <c r="F25">
-        <f t="shared" ref="F25:F26" si="7">E25+$S$2</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26">
-        <f>B25+8</f>
-        <v>40</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="6"/>
-        <v>54</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="7"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27">
-        <f>B26+8</f>
-        <v>48</v>
-      </c>
-      <c r="C27">
-        <f>B27+$P$2</f>
-        <v>50</v>
-      </c>
-      <c r="D27">
-        <f>C27+$Q$2</f>
-        <v>58</v>
-      </c>
-      <c r="E27">
-        <f>D27+$R$2</f>
+      <c r="R34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="83"/>
+    </row>
+    <row r="35" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="87"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="88"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="77"/>
+      <c r="Q35" s="76"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="77"/>
+    </row>
+    <row r="36" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="87"/>
+      <c r="D36" s="88"/>
+      <c r="E36" s="88"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="77"/>
+      <c r="Q36" s="76"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="77"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="C37" s="76"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="77"/>
+      <c r="Q37" s="76"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="77"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="C38" s="76"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="77"/>
+      <c r="Q38" s="76"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="77"/>
+    </row>
+    <row r="39" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="76"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="77"/>
+      <c r="Q39" s="76"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="77"/>
+    </row>
+    <row r="40" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="87">
         <v>62</v>
       </c>
-      <c r="F27">
-        <f>E27+$S$2</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28">
-        <f>D30-2</f>
-        <v>103</v>
-      </c>
-      <c r="C28">
-        <f>B28+$P$2</f>
-        <v>105</v>
-      </c>
-      <c r="D28">
-        <f>C28+$Q$2</f>
-        <v>113</v>
-      </c>
-      <c r="E28">
-        <f>D28+$R$2</f>
-        <v>117</v>
-      </c>
-      <c r="F28">
-        <f>E28+$S$2</f>
-        <v>121</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29">
-        <f>B12+8</f>
-        <v>87</v>
-      </c>
-      <c r="C29">
-        <f>B29+$P$2</f>
-        <v>89</v>
-      </c>
-      <c r="D29">
-        <f>C29+$Q$2</f>
-        <v>97</v>
-      </c>
-      <c r="E29">
-        <f>D29+$R$2</f>
-        <v>101</v>
-      </c>
-      <c r="F29">
-        <f>E29+$S$2</f>
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30">
-        <f>B29+8</f>
-        <v>95</v>
-      </c>
-      <c r="C30">
-        <f>B30+$P$2</f>
-        <v>97</v>
-      </c>
-      <c r="D30">
-        <f>C30+$Q$2</f>
-        <v>105</v>
-      </c>
-      <c r="E30">
-        <f>D30+$R$2</f>
-        <v>109</v>
-      </c>
-      <c r="F30">
-        <f>E30+$S$2</f>
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>196</v>
-      </c>
-      <c r="B31">
-        <f>D27-2</f>
-        <v>56</v>
-      </c>
-      <c r="C31">
-        <f>B31+$Y$2</f>
-        <v>58</v>
-      </c>
-      <c r="D31">
-        <f>C31+$Z$2</f>
-        <v>81</v>
-      </c>
-      <c r="E31" s="51">
-        <f>D31+$AA$2+24</f>
-        <v>97</v>
-      </c>
-      <c r="F31">
-        <f>E31+$AB$2</f>
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32">
-        <f>D16-2</f>
-        <v>135</v>
-      </c>
-      <c r="C32">
-        <f>B32+$P$2</f>
-        <v>137</v>
-      </c>
-      <c r="D32">
-        <f>C32+$Q$2</f>
-        <v>145</v>
-      </c>
-      <c r="E32">
-        <f>D32+$R$2</f>
-        <v>149</v>
-      </c>
-      <c r="F32">
-        <f>E32+$S$2</f>
-        <v>153</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33">
-        <f>B32+8</f>
-        <v>143</v>
-      </c>
-      <c r="C33">
-        <f>B33+$P$2</f>
-        <v>145</v>
-      </c>
-      <c r="D33">
-        <f>C33+$Q$2</f>
-        <v>153</v>
-      </c>
-      <c r="E33">
-        <f>D33+$R$2</f>
-        <v>157</v>
-      </c>
-      <c r="F33">
-        <f>E33+$S$2</f>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34">
-        <f>D33-2</f>
-        <v>151</v>
-      </c>
-      <c r="C34">
-        <f>B34+$P$2</f>
-        <v>153</v>
-      </c>
-      <c r="D34">
-        <f>C34+$Q$2</f>
-        <v>161</v>
-      </c>
-      <c r="E34">
-        <f>D34+$R$2</f>
-        <v>165</v>
-      </c>
-      <c r="F34">
-        <f>E34+$S$2</f>
-        <v>169</v>
+      <c r="D40" s="88"/>
+      <c r="E40" s="88"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="84">
+        <v>63</v>
+      </c>
+      <c r="H40" s="85"/>
+      <c r="I40" s="85"/>
+      <c r="J40" s="86"/>
+      <c r="Q40" s="87">
+        <v>15</v>
+      </c>
+      <c r="R40" s="88"/>
+      <c r="S40" s="88"/>
+      <c r="T40" s="89"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>334</v>
+      </c>
+      <c r="C42" t="s">
+        <v>335</v>
+      </c>
+      <c r="O42" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="86">
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="AY3:AZ6"/>
+    <mergeCell ref="BA3:BB6"/>
+    <mergeCell ref="AY7:AZ10"/>
+    <mergeCell ref="BA7:BB10"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="Q33:T33"/>
+    <mergeCell ref="Q34:T34"/>
+    <mergeCell ref="Q40:T40"/>
+    <mergeCell ref="AN13:AQ13"/>
+    <mergeCell ref="AE14:AH15"/>
+    <mergeCell ref="AE16:AH17"/>
+    <mergeCell ref="AE18:AH19"/>
+    <mergeCell ref="AE20:AH21"/>
+    <mergeCell ref="AI14:AL15"/>
+    <mergeCell ref="AI16:AL17"/>
+    <mergeCell ref="AI18:AL19"/>
+    <mergeCell ref="AI20:AL21"/>
+    <mergeCell ref="AT14:AU15"/>
+    <mergeCell ref="AR16:AS17"/>
+    <mergeCell ref="AT16:AU17"/>
+    <mergeCell ref="AR18:AS19"/>
+    <mergeCell ref="AT18:AU19"/>
+    <mergeCell ref="AT20:AU21"/>
+    <mergeCell ref="AR20:AS21"/>
+    <mergeCell ref="AN16:AO17"/>
+    <mergeCell ref="AN18:AO19"/>
+    <mergeCell ref="AP18:AQ19"/>
+    <mergeCell ref="AN20:AO21"/>
+    <mergeCell ref="AP20:AQ21"/>
+    <mergeCell ref="AR14:AS15"/>
+    <mergeCell ref="AN14:AO15"/>
+    <mergeCell ref="AP14:AQ15"/>
+    <mergeCell ref="AP16:AQ17"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="V13:Y13"/>
+    <mergeCell ref="V14:Y14"/>
+    <mergeCell ref="V15:Y15"/>
+    <mergeCell ref="V16:Y16"/>
+    <mergeCell ref="V20:Y20"/>
+    <mergeCell ref="AE13:AH13"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="AC1:AV1"/>
+    <mergeCell ref="AE3:AH4"/>
+    <mergeCell ref="AJ3:AK6"/>
+    <mergeCell ref="AL3:AM6"/>
+    <mergeCell ref="AE5:AH6"/>
+    <mergeCell ref="AE7:AH8"/>
+    <mergeCell ref="AJ7:AK10"/>
+    <mergeCell ref="AL7:AM10"/>
+    <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C3:F4"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="H3:I6"/>
+    <mergeCell ref="H7:I10"/>
+    <mergeCell ref="J3:K6"/>
+    <mergeCell ref="C5:F6"/>
+    <mergeCell ref="C7:F8"/>
+    <mergeCell ref="J7:K10"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE2FF07-9C06-44AB-97DD-D040F2BA4086}">
   <dimension ref="A1:P32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -12121,7 +13017,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I1" t="str">
         <f>v0!K61</f>
@@ -12290,7 +13186,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -12403,7 +13299,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C7">
         <f>F6</f>
@@ -12452,7 +13348,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C8">
         <f>F7</f>
@@ -12525,11 +13421,11 @@
       </c>
       <c r="I9">
         <f>v0!K69</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <f>v0!L69</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K9">
         <f>v0!M69</f>
@@ -12557,7 +13453,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B10">
         <f>F9</f>
@@ -12614,7 +13510,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C11">
         <f>F10</f>
@@ -12667,7 +13563,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C12">
         <f>F11</f>
@@ -12773,7 +13669,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B14">
         <f>F13</f>
@@ -12830,7 +13726,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C15">
         <f>F14</f>
@@ -12883,7 +13779,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C16">
         <f>F15</f>
@@ -12989,7 +13885,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B18">
         <f>F17</f>
@@ -13046,7 +13942,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C19">
         <f>F18</f>
@@ -13099,7 +13995,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C20">
         <f>F19</f>
@@ -13207,7 +14103,7 @@
       <c r="A22" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="51">
+      <c r="B22" s="54">
         <f>B10-J$11</f>
         <v>44</v>
       </c>
@@ -13264,7 +14160,7 @@
       <c r="A23" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="51">
+      <c r="B23" s="54">
         <f>B14-J$11</f>
         <v>88</v>
       </c>
@@ -13321,7 +14217,7 @@
       <c r="A24" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="51">
+      <c r="B24" s="54">
         <f>B18-J$11</f>
         <v>132</v>
       </c>
@@ -13376,7 +14272,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E25">
         <f>E5+1</f>
@@ -13421,7 +14317,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E26">
         <f>E6+1</f>
@@ -13466,7 +14362,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E27">
         <f>E10+1</f>
@@ -13479,7 +14375,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E28">
         <f>E22+1</f>
@@ -13492,7 +14388,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E29">
         <f>E14+1</f>
@@ -13505,7 +14401,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E30">
         <f>E23+1</f>
@@ -13518,7 +14414,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E31">
         <f>E18+1</f>
@@ -13531,7 +14427,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E32">
         <f>E24+1</f>
@@ -13549,7 +14445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B6543F-8921-434D-8066-C23E3B225BD9}">
   <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -13564,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I1" t="str">
         <f>v0!K61</f>
@@ -13733,25 +14629,21 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <f>B5+I$11</f>
-        <v>13</v>
+        <f>B5+I9</f>
+        <v>6</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:F6" si="0">C5+J$11</f>
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D5:F5" si="0">C5+J9</f>
+        <v>28</v>
+      </c>
+      <c r="E5" s="65">
+        <f>D5+K9+2</f>
         <v>30</v>
       </c>
       <c r="I5">
@@ -13789,27 +14681,23 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="B6">
-        <f>D5-2</f>
-        <v>18</v>
+        <f>D5-2+20</f>
+        <v>46</v>
       </c>
       <c r="C6">
-        <f>B6+I$11</f>
-        <v>20</v>
+        <f>B6+I9</f>
+        <v>48</v>
       </c>
       <c r="D6">
-        <f t="shared" ref="D6" si="1">C6+J$11</f>
-        <v>27</v>
+        <f t="shared" ref="D6:F6" si="1">C6+J9</f>
+        <v>70</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6" si="2">D6+K$11</f>
-        <v>33</v>
-      </c>
-      <c r="F6">
-        <f t="shared" ref="F6" si="3">E6+L$11</f>
-        <v>37</v>
+        <f t="shared" si="1"/>
+        <v>70</v>
       </c>
       <c r="I6" t="str">
         <f>v0!K66</f>
@@ -13848,25 +14736,13 @@
       <c r="A7" t="s">
         <v>235</v>
       </c>
-      <c r="B7">
-        <f t="shared" ref="B7:B8" si="4">D6-2</f>
-        <v>25</v>
-      </c>
-      <c r="C7">
-        <f t="shared" ref="C7:C8" si="5">B7+I$11</f>
-        <v>27</v>
-      </c>
-      <c r="D7">
-        <f t="shared" ref="D7:D8" si="6">C7+J$11</f>
+      <c r="E7">
+        <f>E5</f>
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <f>E7+L$11</f>
         <v>34</v>
-      </c>
-      <c r="E7">
-        <f t="shared" ref="E7:E8" si="7">D7+K$11</f>
-        <v>40</v>
-      </c>
-      <c r="F7">
-        <f t="shared" ref="F7:F8" si="8">E7+L$11</f>
-        <v>44</v>
       </c>
       <c r="I7">
         <f>v0!K67</f>
@@ -13905,25 +14781,13 @@
       <c r="A8" t="s">
         <v>236</v>
       </c>
-      <c r="B8">
-        <f>D7-2</f>
-        <v>32</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="5"/>
+      <c r="E8">
+        <f>F7</f>
         <v>34</v>
       </c>
-      <c r="D8">
-        <f t="shared" si="6"/>
-        <v>41</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="7"/>
-        <v>47</v>
-      </c>
       <c r="F8">
-        <f t="shared" si="8"/>
-        <v>51</v>
+        <f>E8+L$11</f>
+        <v>38</v>
       </c>
       <c r="I8" t="str">
         <f>v0!K68</f>
@@ -13960,42 +14824,31 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>229</v>
-      </c>
-      <c r="B9" s="62">
-        <f>D8-2+16</f>
-        <v>55</v>
-      </c>
-      <c r="C9">
-        <f t="shared" ref="C9" si="9">B9+I$11</f>
-        <v>57</v>
-      </c>
-      <c r="D9">
-        <f t="shared" ref="D9" si="10">C9+J$11</f>
-        <v>64</v>
+        <v>237</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9" si="11">D9+K$11</f>
-        <v>70</v>
+        <f t="shared" ref="E9:E10" si="2">F8</f>
+        <v>38</v>
       </c>
       <c r="F9">
-        <f t="shared" ref="F9" si="12">E9+L$11</f>
-        <v>74</v>
+        <f t="shared" ref="F9:F10" si="3">E9+L$11</f>
+        <v>42</v>
       </c>
       <c r="I9">
         <f>v0!K69</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <f>v0!L69</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K9">
         <f>v0!M69</f>
         <v>0</v>
       </c>
       <c r="L9">
-        <v>24</v>
+        <f>v0!N69</f>
+        <v>20</v>
       </c>
       <c r="M9">
         <f>v0!O69</f>
@@ -14016,27 +14869,15 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B10">
-        <f t="shared" ref="B10:B12" si="13">D9-2</f>
-        <v>62</v>
-      </c>
-      <c r="C10">
-        <f t="shared" ref="C10:C12" si="14">B10+I$11</f>
-        <v>64</v>
-      </c>
-      <c r="D10">
-        <f t="shared" ref="D10:D17" si="15">C10+J$11</f>
-        <v>71</v>
+        <v>238</v>
       </c>
       <c r="E10">
-        <f t="shared" ref="E10:E17" si="16">D10+K$11</f>
-        <v>77</v>
+        <f t="shared" si="2"/>
+        <v>42</v>
       </c>
       <c r="F10">
-        <f t="shared" ref="F10:F17" si="17">E10+L$11</f>
-        <v>81</v>
+        <f>E10+L$11+4</f>
+        <v>50</v>
       </c>
       <c r="I10" t="str">
         <f>v0!K70</f>
@@ -14075,25 +14916,14 @@
       <c r="A11" t="s">
         <v>231</v>
       </c>
-      <c r="B11">
-        <f>D10-2+30</f>
-        <v>99</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="14"/>
-        <v>101</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="15"/>
-        <v>108</v>
-      </c>
+      <c r="B11" s="68"/>
       <c r="E11">
-        <f t="shared" si="16"/>
-        <v>114</v>
+        <f>E6</f>
+        <v>70</v>
       </c>
       <c r="F11">
-        <f t="shared" si="17"/>
-        <v>118</v>
+        <f>E11+L$11</f>
+        <v>74</v>
       </c>
       <c r="I11">
         <f>v0!K71</f>
@@ -14132,25 +14962,13 @@
       <c r="A12" t="s">
         <v>232</v>
       </c>
-      <c r="B12">
-        <f t="shared" si="13"/>
-        <v>106</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="14"/>
-        <v>108</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="15"/>
-        <v>115</v>
-      </c>
       <c r="E12">
-        <f t="shared" si="16"/>
-        <v>121</v>
+        <f>F11</f>
+        <v>74</v>
       </c>
       <c r="F12">
-        <f t="shared" si="17"/>
-        <v>125</v>
+        <f t="shared" ref="F12:F14" si="4">E12+L$11</f>
+        <v>78</v>
       </c>
       <c r="I12" t="str">
         <f>v0!K72</f>
@@ -14187,15 +15005,15 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E13">
-        <f>E5+1</f>
-        <v>27</v>
+        <f t="shared" ref="E13:E14" si="5">F12</f>
+        <v>78</v>
       </c>
       <c r="F13">
-        <f>F5+1</f>
-        <v>31</v>
+        <f t="shared" ref="F13:F14" si="6">E13+L$11</f>
+        <v>82</v>
       </c>
       <c r="I13">
         <f>v0!K73</f>
@@ -14232,15 +15050,15 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14:F20" si="18">E6+1</f>
-        <v>34</v>
+        <f t="shared" si="5"/>
+        <v>82</v>
       </c>
       <c r="F14">
-        <f t="shared" si="18"/>
-        <v>38</v>
+        <f>E14+L$11+4</f>
+        <v>90</v>
       </c>
       <c r="I14" t="str">
         <f>v0!K74</f>
@@ -14280,12 +15098,12 @@
         <v>250</v>
       </c>
       <c r="E15">
-        <f t="shared" si="18"/>
-        <v>41</v>
+        <f>E7+1</f>
+        <v>31</v>
       </c>
       <c r="F15">
-        <f t="shared" si="18"/>
-        <v>45</v>
+        <f>F7+1</f>
+        <v>35</v>
       </c>
       <c r="I15">
         <f>v0!K75</f>
@@ -14325,12 +15143,12 @@
         <v>251</v>
       </c>
       <c r="E16">
-        <f t="shared" si="18"/>
-        <v>48</v>
+        <f t="shared" ref="E16:F22" si="7">E8+1</f>
+        <v>35</v>
       </c>
       <c r="F16">
-        <f t="shared" si="18"/>
-        <v>52</v>
+        <f t="shared" si="7"/>
+        <v>39</v>
       </c>
       <c r="I16" t="str">
         <f>v0!K76</f>
@@ -14370,12 +15188,12 @@
         <v>252</v>
       </c>
       <c r="E17">
-        <f t="shared" si="18"/>
-        <v>71</v>
+        <f t="shared" si="7"/>
+        <v>39</v>
       </c>
       <c r="F17">
-        <f t="shared" si="18"/>
-        <v>75</v>
+        <f t="shared" si="7"/>
+        <v>43</v>
       </c>
       <c r="I17">
         <f>v0!K77</f>
@@ -14415,12 +15233,12 @@
         <v>253</v>
       </c>
       <c r="E18">
-        <f t="shared" si="18"/>
-        <v>78</v>
+        <f t="shared" si="7"/>
+        <v>43</v>
       </c>
       <c r="F18">
-        <f t="shared" si="18"/>
-        <v>82</v>
+        <f t="shared" si="7"/>
+        <v>51</v>
       </c>
       <c r="I18" t="str">
         <f>v0!K78</f>
@@ -14460,12 +15278,12 @@
         <v>254</v>
       </c>
       <c r="E19">
-        <f t="shared" si="18"/>
-        <v>115</v>
+        <f t="shared" si="7"/>
+        <v>71</v>
       </c>
       <c r="F19">
-        <f t="shared" si="18"/>
-        <v>119</v>
+        <f t="shared" si="7"/>
+        <v>75</v>
       </c>
       <c r="I19">
         <f>v0!K79</f>
@@ -14505,12 +15323,12 @@
         <v>255</v>
       </c>
       <c r="E20">
-        <f t="shared" si="18"/>
-        <v>122</v>
+        <f t="shared" si="7"/>
+        <v>75</v>
       </c>
       <c r="F20">
-        <f t="shared" si="18"/>
-        <v>126</v>
+        <f t="shared" si="7"/>
+        <v>79</v>
       </c>
       <c r="I20">
         <f>v0!K80</f>
@@ -14546,6 +15364,17 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>256</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="7"/>
+        <v>79</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="7"/>
+        <v>83</v>
+      </c>
       <c r="I21">
         <f>v0!K81</f>
         <v>0</v>
@@ -14580,6 +15409,17 @@
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>257</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="7"/>
+        <v>83</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="7"/>
+        <v>91</v>
+      </c>
       <c r="I22">
         <f>v0!K82</f>
         <v>0</v>
@@ -14755,7 +15595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A8745C-91F1-4442-962E-DE64FDFDAC26}">
   <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -14774,7 +15614,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I1" t="str">
         <f>v0!K61</f>
@@ -14943,7 +15783,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -14999,7 +15839,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B6">
         <f>D5-2</f>
@@ -15056,7 +15896,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C7">
         <f>F6</f>
@@ -15108,7 +15948,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C8">
         <f>F7</f>
@@ -15181,11 +16021,11 @@
       </c>
       <c r="I9">
         <f>v0!K69</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <f>v0!L69</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K9">
         <f>v0!M69</f>
@@ -15213,7 +16053,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B10">
         <f>'264PMF Y c0 round0'!B10</f>
@@ -15270,7 +16110,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C11">
         <f>F10</f>
@@ -15323,7 +16163,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C12">
         <f>F11</f>
@@ -15429,7 +16269,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B14">
         <f>'264PMF Y c0 round0'!B14</f>
@@ -15486,7 +16326,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C15">
         <f>F14</f>
@@ -15539,7 +16379,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C16">
         <f>F15</f>
@@ -15645,7 +16485,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B18">
         <f>'264PMF Y c0 round0'!B18</f>
@@ -15702,7 +16542,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C19">
         <f>F18</f>
@@ -15755,7 +16595,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C20">
         <f>F19</f>
@@ -15975,7 +16815,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B24">
         <f>B18-J19</f>
@@ -16104,7 +16944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF15CD4-0F23-4B5D-858D-80243844B2B7}">
   <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -16119,7 +16959,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I1" t="str">
         <f>v0!K61</f>
@@ -16288,26 +17128,22 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B5" s="62">
-        <v>6</v>
+        <v>220</v>
+      </c>
+      <c r="B5" s="64">
+        <v>0</v>
       </c>
       <c r="C5">
-        <f>B5+I$17</f>
-        <v>8</v>
+        <f>B5+I17</f>
+        <v>2</v>
       </c>
       <c r="D5">
-        <f>C5+J$17</f>
-        <v>24</v>
+        <f t="shared" ref="D5:F5" si="0">C5+J17</f>
+        <v>20</v>
       </c>
       <c r="E5">
-        <f>D5+K$17</f>
+        <f>D5+K17+4</f>
         <v>30</v>
-      </c>
-      <c r="F5">
-        <f>E5+L$17</f>
-        <v>38</v>
       </c>
       <c r="I5">
         <f>v0!K65</f>
@@ -16344,27 +17180,23 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B6">
+        <v>221</v>
+      </c>
+      <c r="B6" s="64">
         <f>D5-2</f>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <f>B6+I$17</f>
-        <v>24</v>
+        <f>B6+I17</f>
+        <v>20</v>
       </c>
       <c r="D6">
-        <f>C6+J$17</f>
-        <v>40</v>
+        <f t="shared" ref="D6:F6" si="1">C6+J17</f>
+        <v>38</v>
       </c>
       <c r="E6">
-        <f>D6+K$17</f>
-        <v>46</v>
-      </c>
-      <c r="F6">
-        <f>E6+L$17</f>
-        <v>54</v>
+        <f t="shared" si="1"/>
+        <v>44</v>
       </c>
       <c r="I6" t="str">
         <f>v0!K66</f>
@@ -16401,27 +17233,16 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="62">
-        <f>D6-2+7</f>
-        <v>45</v>
-      </c>
-      <c r="C7">
-        <f>B7+I$17</f>
-        <v>47</v>
-      </c>
-      <c r="D7">
-        <f>C7+J$17</f>
-        <v>63</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="B7" s="64"/>
       <c r="E7">
-        <f>D7+K$17</f>
-        <v>69</v>
+        <f>E5+1</f>
+        <v>31</v>
       </c>
       <c r="F7">
-        <f>E7+L$17</f>
-        <v>77</v>
+        <f>E7+2</f>
+        <v>33</v>
       </c>
       <c r="I7">
         <f>v0!K67</f>
@@ -16460,25 +17281,14 @@
       <c r="A8" t="s">
         <v>244</v>
       </c>
-      <c r="B8" s="61">
-        <f t="shared" ref="B7:B12" si="0">D7-2</f>
-        <v>61</v>
-      </c>
-      <c r="C8">
-        <f>B8+I$17</f>
-        <v>63</v>
-      </c>
-      <c r="D8">
-        <f>C8+J$17</f>
-        <v>79</v>
-      </c>
+      <c r="B8" s="64"/>
       <c r="E8">
-        <f>D8+K$17</f>
-        <v>85</v>
+        <f>F7</f>
+        <v>33</v>
       </c>
       <c r="F8">
-        <f>E8+L$17</f>
-        <v>93</v>
+        <f t="shared" ref="F8:F9" si="2">E8+2</f>
+        <v>35</v>
       </c>
       <c r="I8" t="str">
         <f>v0!K68</f>
@@ -16515,35 +17325,24 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>240</v>
-      </c>
-      <c r="B9" s="62">
-        <f>D8-2+12</f>
-        <v>89</v>
-      </c>
-      <c r="C9">
-        <f>B9+I$17</f>
-        <v>91</v>
-      </c>
-      <c r="D9">
-        <f>C9+J$17</f>
-        <v>107</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="B9" s="64"/>
       <c r="E9">
-        <f>D9+K$17</f>
-        <v>113</v>
+        <f t="shared" ref="E9:E14" si="3">F8</f>
+        <v>35</v>
       </c>
       <c r="F9">
-        <f>E9+L$17</f>
-        <v>121</v>
+        <f t="shared" si="2"/>
+        <v>37</v>
       </c>
       <c r="I9">
         <f>v0!K69</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <f>v0!L69</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K9">
         <f>v0!M69</f>
@@ -16571,27 +17370,16 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>245</v>
-      </c>
-      <c r="B10">
-        <f t="shared" si="0"/>
-        <v>105</v>
-      </c>
-      <c r="C10">
-        <f>B10+I$17</f>
-        <v>107</v>
-      </c>
-      <c r="D10">
-        <f>C10+J$17</f>
-        <v>123</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="B10" s="64"/>
       <c r="E10">
-        <f>D10+K$17</f>
-        <v>129</v>
+        <f t="shared" si="3"/>
+        <v>37</v>
       </c>
       <c r="F10">
-        <f>E10+L$17</f>
-        <v>137</v>
+        <f>E10+4</f>
+        <v>41</v>
       </c>
       <c r="I10" t="str">
         <f>v0!K70</f>
@@ -16628,27 +17416,16 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B11" s="62">
-        <f>D10-2+12</f>
-        <v>133</v>
-      </c>
-      <c r="C11">
-        <f>B11+I$17</f>
-        <v>135</v>
-      </c>
-      <c r="D11">
-        <f>C11+J$17</f>
-        <v>151</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="B11" s="64"/>
       <c r="E11">
-        <f>D11+K$17</f>
-        <v>157</v>
+        <f>E6+1</f>
+        <v>45</v>
       </c>
       <c r="F11">
-        <f>E11+L$17</f>
-        <v>165</v>
+        <f>E11+2</f>
+        <v>47</v>
       </c>
       <c r="I11">
         <f>v0!K71</f>
@@ -16687,25 +17464,14 @@
       <c r="A12" t="s">
         <v>247</v>
       </c>
-      <c r="B12">
-        <f t="shared" si="0"/>
-        <v>149</v>
-      </c>
-      <c r="C12">
-        <f>B12+I$17</f>
-        <v>151</v>
-      </c>
-      <c r="D12">
-        <f>C12+J$17</f>
-        <v>167</v>
-      </c>
+      <c r="B12" s="64"/>
       <c r="E12">
-        <f>D12+K$17</f>
-        <v>173</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F12">
-        <f>E12+L$17</f>
-        <v>181</v>
+        <f t="shared" ref="F12:F13" si="4">E12+2</f>
+        <v>49</v>
       </c>
       <c r="I12" t="str">
         <f>v0!K72</f>
@@ -16741,6 +17507,18 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B13" s="64"/>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="4"/>
+        <v>51</v>
+      </c>
       <c r="I13">
         <f>v0!K73</f>
         <v>0</v>
@@ -16775,6 +17553,17 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="F14">
+        <f>E14+4</f>
+        <v>55</v>
+      </c>
       <c r="I14" t="str">
         <f>v0!K74</f>
         <v>UVread latancy</v>
@@ -16882,8 +17671,7 @@
         <v>2</v>
       </c>
       <c r="J17">
-        <f>v0!L77</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17">
         <f>v0!M77</f>
@@ -17214,6 +18002,894 @@
       <c r="P26">
         <f>v0!R86</f>
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A37FD03-BF78-46BE-832D-3A5B174965E9}">
+  <dimension ref="A1:AB34"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" t="str">
+        <f>v0!A62</f>
+        <v>inter pk in</v>
+      </c>
+      <c r="I1" t="str">
+        <f>v0!B62</f>
+        <v>inter pk work</v>
+      </c>
+      <c r="J1" t="str">
+        <f>v0!C62</f>
+        <v>inter pk out</v>
+      </c>
+      <c r="L1" t="str">
+        <f>v0!A64</f>
+        <v>sel pk in</v>
+      </c>
+      <c r="M1" t="str">
+        <f>v0!B64</f>
+        <v>sel pk work</v>
+      </c>
+      <c r="N1" t="str">
+        <f>v0!C64</f>
+        <v>sel pk out</v>
+      </c>
+      <c r="P1" t="str">
+        <f>v0!A70</f>
+        <v>Yread latancy</v>
+      </c>
+      <c r="Q1" t="str">
+        <f>v0!B70</f>
+        <v>8x8 input cc</v>
+      </c>
+      <c r="R1" t="str">
+        <f>v0!C70</f>
+        <v>8x8 work cc</v>
+      </c>
+      <c r="S1" t="str">
+        <f>v0!D70</f>
+        <v>8x8 output cc</v>
+      </c>
+      <c r="U1" t="str">
+        <f>v0!G62</f>
+        <v>tqitq8x8 input</v>
+      </c>
+      <c r="V1" t="str">
+        <f>v0!H62</f>
+        <v>tqitq work</v>
+      </c>
+      <c r="W1" t="str">
+        <f>v0!I62</f>
+        <v>tqitq out</v>
+      </c>
+      <c r="Y1" t="str">
+        <f>v0!A68</f>
+        <v>Yread latancy</v>
+      </c>
+      <c r="Z1" t="str">
+        <f>v0!B68</f>
+        <v>16x16 input cc</v>
+      </c>
+      <c r="AA1" t="str">
+        <f>v0!C68</f>
+        <v>16x16 work cc</v>
+      </c>
+      <c r="AB1" t="str">
+        <f>v0!D68</f>
+        <v>16x16 output cc</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <f>v0!A63</f>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <f>v0!B63</f>
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <f>v0!C63</f>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <f>v0!A65</f>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <f>v0!B65</f>
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <f>v0!C65</f>
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <f>v0!A71</f>
+        <v>2</v>
+      </c>
+      <c r="Q2">
+        <f>v0!B71</f>
+        <v>8</v>
+      </c>
+      <c r="R2">
+        <f>v0!C71</f>
+        <v>4</v>
+      </c>
+      <c r="S2">
+        <f>v0!D71</f>
+        <v>4</v>
+      </c>
+      <c r="U2">
+        <f>v0!G63</f>
+        <v>4</v>
+      </c>
+      <c r="V2">
+        <f>v0!H63</f>
+        <v>23</v>
+      </c>
+      <c r="W2">
+        <f>v0!I63</f>
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <f>v0!A69</f>
+        <v>2</v>
+      </c>
+      <c r="Z2">
+        <f>v0!B69</f>
+        <v>23</v>
+      </c>
+      <c r="AA2">
+        <f>v0!C69</f>
+        <v>-8</v>
+      </c>
+      <c r="AB2">
+        <f>v0!D69</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <f>B5+$P$2</f>
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <f>C5+$Q$2</f>
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <f>D5+$R$2</f>
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <f>E5+$S$2</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6">
+        <f>B5+8</f>
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:C8" si="0">B6+$P$2</f>
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D8" si="1">C6+$Q$2</f>
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ref="E6:E8" si="2">D6+$R$2</f>
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <f t="shared" ref="F6:F8" si="3">E6+$S$2</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <f>B6+8</f>
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8">
+        <f>B7+8</f>
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9">
+        <f>E8</f>
+        <v>38</v>
+      </c>
+      <c r="D9">
+        <f>C9+$U$2</f>
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <f>D9+$V$2</f>
+        <v>65</v>
+      </c>
+      <c r="F9">
+        <f>E9+$W$2</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <f>F9</f>
+        <v>66</v>
+      </c>
+      <c r="D10">
+        <f>C10+$H$2</f>
+        <v>67</v>
+      </c>
+      <c r="E10">
+        <f>D10+$I$2</f>
+        <v>68</v>
+      </c>
+      <c r="F10">
+        <f>E10+$J$2</f>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11">
+        <f>F10</f>
+        <v>69</v>
+      </c>
+      <c r="D11">
+        <f>C11+$L$2</f>
+        <v>70</v>
+      </c>
+      <c r="E11">
+        <f>D11+$M$2</f>
+        <v>71</v>
+      </c>
+      <c r="F11">
+        <f>E11+$N$2</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <f>D31-2</f>
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <f>B12+$P$2</f>
+        <v>81</v>
+      </c>
+      <c r="D12">
+        <f>C12+$Q$2</f>
+        <v>89</v>
+      </c>
+      <c r="E12">
+        <f>D12+$R$2</f>
+        <v>93</v>
+      </c>
+      <c r="F12">
+        <f>E12+$S$2</f>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13">
+        <f>E12</f>
+        <v>93</v>
+      </c>
+      <c r="D13">
+        <f>C13+$U$2</f>
+        <v>97</v>
+      </c>
+      <c r="E13">
+        <f>D13+$V$2</f>
+        <v>120</v>
+      </c>
+      <c r="F13">
+        <f>E13+$W$2</f>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14">
+        <f>F13</f>
+        <v>121</v>
+      </c>
+      <c r="D14">
+        <f>C14+$H$2</f>
+        <v>122</v>
+      </c>
+      <c r="E14">
+        <f>D14+$I$2</f>
+        <v>123</v>
+      </c>
+      <c r="F14">
+        <f>E14+$J$2</f>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15">
+        <f>F14</f>
+        <v>124</v>
+      </c>
+      <c r="D15">
+        <f>C15+$L$2</f>
+        <v>125</v>
+      </c>
+      <c r="E15">
+        <f>D15+$M$2</f>
+        <v>126</v>
+      </c>
+      <c r="F15">
+        <f>E15+$N$2</f>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16">
+        <f>F15</f>
+        <v>127</v>
+      </c>
+      <c r="C16">
+        <f>B16+$P$2</f>
+        <v>129</v>
+      </c>
+      <c r="D16">
+        <f>C16+$Q$2</f>
+        <v>137</v>
+      </c>
+      <c r="E16">
+        <f>D16+$R$2</f>
+        <v>141</v>
+      </c>
+      <c r="F16">
+        <f>E16+$S$2</f>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17">
+        <f>E16</f>
+        <v>141</v>
+      </c>
+      <c r="D17">
+        <f>C17+$U$2</f>
+        <v>145</v>
+      </c>
+      <c r="E17">
+        <f>D17+$V$2</f>
+        <v>168</v>
+      </c>
+      <c r="F17">
+        <f>E17+$W$2</f>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18">
+        <f>F17</f>
+        <v>169</v>
+      </c>
+      <c r="D18">
+        <f>C18+$H$2</f>
+        <v>170</v>
+      </c>
+      <c r="E18">
+        <f>D18+$I$2</f>
+        <v>171</v>
+      </c>
+      <c r="F18">
+        <f>E18+$J$2</f>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19">
+        <f>F18</f>
+        <v>172</v>
+      </c>
+      <c r="D19">
+        <f>C19+$L$2</f>
+        <v>173</v>
+      </c>
+      <c r="E19">
+        <f>D19+$M$2</f>
+        <v>174</v>
+      </c>
+      <c r="F19">
+        <f>E19+$N$2</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20">
+        <f>F19</f>
+        <v>175</v>
+      </c>
+      <c r="C20">
+        <f>B20+$P$2</f>
+        <v>177</v>
+      </c>
+      <c r="D20">
+        <f>C20+$Q$2</f>
+        <v>185</v>
+      </c>
+      <c r="E20">
+        <f>D20+$R$2</f>
+        <v>189</v>
+      </c>
+      <c r="F20">
+        <f>E20+$S$2</f>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21">
+        <f>E20</f>
+        <v>189</v>
+      </c>
+      <c r="D21">
+        <f>C21+$U$2</f>
+        <v>193</v>
+      </c>
+      <c r="E21">
+        <f>D21+$V$2</f>
+        <v>216</v>
+      </c>
+      <c r="F21">
+        <f>E21+$W$2</f>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22">
+        <f>F21</f>
+        <v>217</v>
+      </c>
+      <c r="D22">
+        <f>C22+$H$2</f>
+        <v>218</v>
+      </c>
+      <c r="E22">
+        <f>D22+$I$2</f>
+        <v>219</v>
+      </c>
+      <c r="F22">
+        <f>E22+$J$2</f>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23">
+        <f>F22</f>
+        <v>220</v>
+      </c>
+      <c r="D23">
+        <f>C23+$L$2</f>
+        <v>221</v>
+      </c>
+      <c r="E23">
+        <f>D23+$M$2</f>
+        <v>222</v>
+      </c>
+      <c r="F23">
+        <f>E23+$N$2</f>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24">
+        <f>F23</f>
+        <v>223</v>
+      </c>
+      <c r="E24">
+        <f>D24+7</f>
+        <v>230</v>
+      </c>
+      <c r="F24">
+        <f>E24+1</f>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25">
+        <f>B8+8</f>
+        <v>32</v>
+      </c>
+      <c r="C25">
+        <f t="shared" ref="C25:C26" si="4">B25+$P$2</f>
+        <v>34</v>
+      </c>
+      <c r="D25">
+        <f t="shared" ref="D25:D26" si="5">C25+$Q$2</f>
+        <v>42</v>
+      </c>
+      <c r="E25">
+        <f t="shared" ref="E25:E26" si="6">D25+$R$2</f>
+        <v>46</v>
+      </c>
+      <c r="F25">
+        <f t="shared" ref="F25:F26" si="7">E25+$S$2</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <f>B25+8</f>
+        <v>40</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="4"/>
+        <v>42</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="6"/>
+        <v>54</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="7"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27">
+        <f>B26+8</f>
+        <v>48</v>
+      </c>
+      <c r="C27">
+        <f>B27+$P$2</f>
+        <v>50</v>
+      </c>
+      <c r="D27">
+        <f>C27+$Q$2</f>
+        <v>58</v>
+      </c>
+      <c r="E27">
+        <f>D27+$R$2</f>
+        <v>62</v>
+      </c>
+      <c r="F27">
+        <f>E27+$S$2</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28">
+        <f>D30-2</f>
+        <v>103</v>
+      </c>
+      <c r="C28">
+        <f>B28+$P$2</f>
+        <v>105</v>
+      </c>
+      <c r="D28">
+        <f>C28+$Q$2</f>
+        <v>113</v>
+      </c>
+      <c r="E28">
+        <f>D28+$R$2</f>
+        <v>117</v>
+      </c>
+      <c r="F28">
+        <f>E28+$S$2</f>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29">
+        <f>B12+8</f>
+        <v>87</v>
+      </c>
+      <c r="C29">
+        <f>B29+$P$2</f>
+        <v>89</v>
+      </c>
+      <c r="D29">
+        <f>C29+$Q$2</f>
+        <v>97</v>
+      </c>
+      <c r="E29">
+        <f>D29+$R$2</f>
+        <v>101</v>
+      </c>
+      <c r="F29">
+        <f>E29+$S$2</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30">
+        <f>B29+8</f>
+        <v>95</v>
+      </c>
+      <c r="C30">
+        <f>B30+$P$2</f>
+        <v>97</v>
+      </c>
+      <c r="D30">
+        <f>C30+$Q$2</f>
+        <v>105</v>
+      </c>
+      <c r="E30">
+        <f>D30+$R$2</f>
+        <v>109</v>
+      </c>
+      <c r="F30">
+        <f>E30+$S$2</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B31">
+        <f>D27-2</f>
+        <v>56</v>
+      </c>
+      <c r="C31">
+        <f>B31+$Y$2</f>
+        <v>58</v>
+      </c>
+      <c r="D31">
+        <f>C31+$Z$2</f>
+        <v>81</v>
+      </c>
+      <c r="E31" s="54">
+        <f>D31+$AA$2+24</f>
+        <v>97</v>
+      </c>
+      <c r="F31">
+        <f>E31+$AB$2</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32">
+        <f>D16-2</f>
+        <v>135</v>
+      </c>
+      <c r="C32">
+        <f>B32+$P$2</f>
+        <v>137</v>
+      </c>
+      <c r="D32">
+        <f>C32+$Q$2</f>
+        <v>145</v>
+      </c>
+      <c r="E32">
+        <f>D32+$R$2</f>
+        <v>149</v>
+      </c>
+      <c r="F32">
+        <f>E32+$S$2</f>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33">
+        <f>B32+8</f>
+        <v>143</v>
+      </c>
+      <c r="C33">
+        <f>B33+$P$2</f>
+        <v>145</v>
+      </c>
+      <c r="D33">
+        <f>C33+$Q$2</f>
+        <v>153</v>
+      </c>
+      <c r="E33">
+        <f>D33+$R$2</f>
+        <v>157</v>
+      </c>
+      <c r="F33">
+        <f>E33+$S$2</f>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34">
+        <f>D33-2</f>
+        <v>151</v>
+      </c>
+      <c r="C34">
+        <f>B34+$P$2</f>
+        <v>153</v>
+      </c>
+      <c r="D34">
+        <f>C34+$Q$2</f>
+        <v>161</v>
+      </c>
+      <c r="E34">
+        <f>D34+$R$2</f>
+        <v>165</v>
+      </c>
+      <c r="F34">
+        <f>E34+$S$2</f>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -17305,11 +18981,11 @@
         <f>'PMF c0 round0'!D5</f>
         <v>10</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="52">
         <f>'PMF c0 round0'!E5+2</f>
         <v>16</v>
       </c>
-      <c r="F5" s="49">
+      <c r="F5" s="52">
         <f>'PMF c0 round0'!F5+2</f>
         <v>20</v>
       </c>
@@ -17331,11 +19007,11 @@
         <f>'PMF c0 round0'!D6</f>
         <v>18</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="52">
         <f>'PMF c0 round0'!E6+2</f>
         <v>24</v>
       </c>
-      <c r="F6" s="49">
+      <c r="F6" s="52">
         <f>'PMF c0 round0'!F6+2</f>
         <v>28</v>
       </c>
@@ -17357,11 +19033,11 @@
         <f>'PMF c0 round0'!D7</f>
         <v>26</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="52">
         <f>'PMF c0 round0'!E7+2</f>
         <v>32</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="52">
         <f>'PMF c0 round0'!F7+2</f>
         <v>36</v>
       </c>
@@ -17383,11 +19059,11 @@
         <f>'PMF c0 round0'!D8</f>
         <v>34</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="52">
         <f>'PMF c0 round0'!E8+2</f>
         <v>40</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="52">
         <f>'PMF c0 round0'!F8+2</f>
         <v>44</v>
       </c>
@@ -17487,11 +19163,11 @@
         <f>'PMF c0 round0'!D12</f>
         <v>89</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="52">
         <f>'PMF c0 round0'!E12+2</f>
         <v>95</v>
       </c>
-      <c r="F12" s="49">
+      <c r="F12" s="52">
         <f>'PMF c0 round0'!F12+2</f>
         <v>99</v>
       </c>
@@ -17591,11 +19267,11 @@
         <f>'PMF c0 round0'!D16</f>
         <v>137</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="52">
         <f>'PMF c0 round0'!E16+2</f>
         <v>143</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="52">
         <f>'PMF c0 round0'!F16+2</f>
         <v>147</v>
       </c>
@@ -17695,11 +19371,11 @@
         <f>'PMF c0 round0'!D20</f>
         <v>185</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="52">
         <f>'PMF c0 round0'!E20+5</f>
         <v>194</v>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="52">
         <f>'PMF c0 round0'!F20+5</f>
         <v>198</v>
       </c>
@@ -17825,11 +19501,11 @@
         <f>'PMF c0 round0'!D25</f>
         <v>42</v>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="52">
         <f>'PMF c0 round0'!E25+2</f>
         <v>48</v>
       </c>
-      <c r="F25" s="49">
+      <c r="F25" s="52">
         <f>'PMF c0 round0'!F25+2</f>
         <v>52</v>
       </c>
@@ -17851,11 +19527,11 @@
         <f>'PMF c0 round0'!D26</f>
         <v>50</v>
       </c>
-      <c r="E26" s="49">
+      <c r="E26" s="52">
         <f>'PMF c0 round0'!E26+2</f>
         <v>56</v>
       </c>
-      <c r="F26" s="49">
+      <c r="F26" s="52">
         <f>'PMF c0 round0'!F26+2</f>
         <v>60</v>
       </c>
@@ -17877,11 +19553,11 @@
         <f>'PMF c0 round0'!D27</f>
         <v>58</v>
       </c>
-      <c r="E27" s="49">
+      <c r="E27" s="52">
         <f>'PMF c0 round0'!E27+2</f>
         <v>64</v>
       </c>
-      <c r="F27" s="49">
+      <c r="F27" s="52">
         <f>'PMF c0 round0'!F27+2</f>
         <v>68</v>
       </c>
@@ -17903,11 +19579,11 @@
         <f>'PMF c0 round0'!D28</f>
         <v>113</v>
       </c>
-      <c r="E28" s="49">
+      <c r="E28" s="52">
         <f>'PMF c0 round0'!E28+2</f>
         <v>119</v>
       </c>
-      <c r="F28" s="49">
+      <c r="F28" s="52">
         <f>'PMF c0 round0'!F28+2</f>
         <v>123</v>
       </c>
@@ -17929,11 +19605,11 @@
         <f>'PMF c0 round0'!D29</f>
         <v>97</v>
       </c>
-      <c r="E29" s="49">
+      <c r="E29" s="52">
         <f>'PMF c0 round0'!E29+2</f>
         <v>103</v>
       </c>
-      <c r="F29" s="49">
+      <c r="F29" s="52">
         <f>'PMF c0 round0'!F29+2</f>
         <v>107</v>
       </c>
@@ -17955,11 +19631,11 @@
         <f>'PMF c0 round0'!D30</f>
         <v>105</v>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="52">
         <f>'PMF c0 round0'!E30+2</f>
         <v>111</v>
       </c>
-      <c r="F30" s="49">
+      <c r="F30" s="52">
         <f>'PMF c0 round0'!F30+2</f>
         <v>115</v>
       </c>
@@ -18007,11 +19683,11 @@
         <f>'PMF c0 round0'!D32</f>
         <v>145</v>
       </c>
-      <c r="E32" s="49">
+      <c r="E32" s="52">
         <f>'PMF c0 round0'!E32+2</f>
         <v>151</v>
       </c>
-      <c r="F32" s="49">
+      <c r="F32" s="52">
         <f>'PMF c0 round0'!F32+2</f>
         <v>155</v>
       </c>
@@ -18033,11 +19709,11 @@
         <f>'PMF c0 round0'!D33</f>
         <v>153</v>
       </c>
-      <c r="E33" s="49">
+      <c r="E33" s="52">
         <f>'PMF c0 round0'!E33+2</f>
         <v>159</v>
       </c>
-      <c r="F33" s="49">
+      <c r="F33" s="52">
         <f>'PMF c0 round0'!F33+2</f>
         <v>163</v>
       </c>
@@ -18059,11 +19735,11 @@
         <f>'PMF c0 round0'!D34</f>
         <v>161</v>
       </c>
-      <c r="E34" s="49">
+      <c r="E34" s="52">
         <f>'PMF c0 round0'!E34+2</f>
         <v>167</v>
       </c>
-      <c r="F34" s="49">
+      <c r="F34" s="52">
         <f>'PMF c0 round0'!F34+2</f>
         <v>171</v>
       </c>
@@ -18309,11 +19985,11 @@
         <f>'PMF c0 round1-3'!D6</f>
         <v>216</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="52">
         <f>'PMF c0 round1-3'!E6+2</f>
         <v>222</v>
       </c>
-      <c r="F5" s="49">
+      <c r="F5" s="52">
         <f>'PMF c0 round1-3'!F6+2</f>
         <v>226</v>
       </c>
@@ -18335,11 +20011,11 @@
         <f>'PMF c0 round1-3'!D7</f>
         <v>224</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="52">
         <f>'PMF c0 round1-3'!E7+2</f>
         <v>230</v>
       </c>
-      <c r="F6" s="49">
+      <c r="F6" s="52">
         <f>'PMF c0 round1-3'!F7+2</f>
         <v>234</v>
       </c>
@@ -18361,11 +20037,11 @@
         <f>'PMF c0 round1-3'!D8</f>
         <v>232</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="52">
         <f>'PMF c0 round1-3'!E8+2</f>
         <v>238</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="52">
         <f>'PMF c0 round1-3'!F8+2</f>
         <v>242</v>
       </c>
@@ -18387,11 +20063,11 @@
         <f>'PMF c0 round1-3'!D9</f>
         <v>240</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="52">
         <f>'PMF c0 round1-3'!E9+2</f>
         <v>246</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="52">
         <f>'PMF c0 round1-3'!F9+2</f>
         <v>250</v>
       </c>
@@ -18491,11 +20167,11 @@
         <f>'PMF c0 round1-3'!D13</f>
         <v>295</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="52">
         <f>'PMF c0 round1-3'!E13+2</f>
         <v>301</v>
       </c>
-      <c r="F12" s="49">
+      <c r="F12" s="52">
         <f>'PMF c0 round1-3'!F13+2</f>
         <v>305</v>
       </c>
@@ -18595,11 +20271,11 @@
         <f>'PMF c0 round1-3'!D17</f>
         <v>343</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="52">
         <f>'PMF c0 round1-3'!E17+1</f>
         <v>348</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="52">
         <f>'PMF c0 round1-3'!F17+1</f>
         <v>352</v>
       </c>
@@ -18699,11 +20375,11 @@
         <f>'PMF c0 round1-3'!D21</f>
         <v>391</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="53">
         <f>'PMF c0 round1-3'!E21+5</f>
         <v>400</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="53">
         <f>'PMF c0 round1-3'!F21+5</f>
         <v>404</v>
       </c>
@@ -18803,11 +20479,11 @@
         <f>'PMF c0 round1-3'!D25</f>
         <v>248</v>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="52">
         <f>'PMF c0 round1-3'!E25+2</f>
         <v>254</v>
       </c>
-      <c r="F24" s="49">
+      <c r="F24" s="52">
         <f>'PMF c0 round1-3'!F25+2</f>
         <v>258</v>
       </c>
@@ -18829,11 +20505,11 @@
         <f>'PMF c0 round1-3'!D26</f>
         <v>256</v>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="52">
         <f>'PMF c0 round1-3'!E26+2</f>
         <v>262</v>
       </c>
-      <c r="F25" s="49">
+      <c r="F25" s="52">
         <f>'PMF c0 round1-3'!F26+2</f>
         <v>266</v>
       </c>
@@ -18855,11 +20531,11 @@
         <f>'PMF c0 round1-3'!D27</f>
         <v>264</v>
       </c>
-      <c r="E26" s="49">
+      <c r="E26" s="52">
         <f>'PMF c0 round1-3'!E27+2</f>
         <v>270</v>
       </c>
-      <c r="F26" s="49">
+      <c r="F26" s="52">
         <f>'PMF c0 round1-3'!F27+2</f>
         <v>274</v>
       </c>
@@ -18881,11 +20557,11 @@
         <f>'PMF c0 round1-3'!D28</f>
         <v>319</v>
       </c>
-      <c r="E27" s="49">
+      <c r="E27" s="52">
         <f>'PMF c0 round1-3'!E28+2</f>
         <v>325</v>
       </c>
-      <c r="F27" s="49">
+      <c r="F27" s="52">
         <f>'PMF c0 round1-3'!F28+2</f>
         <v>329</v>
       </c>
@@ -18907,11 +20583,11 @@
         <f>'PMF c0 round1-3'!D29</f>
         <v>303</v>
       </c>
-      <c r="E28" s="49">
+      <c r="E28" s="52">
         <f>'PMF c0 round1-3'!E29+2</f>
         <v>309</v>
       </c>
-      <c r="F28" s="49">
+      <c r="F28" s="52">
         <f>'PMF c0 round1-3'!F29+2</f>
         <v>313</v>
       </c>
@@ -18933,11 +20609,11 @@
         <f>'PMF c0 round1-3'!D30</f>
         <v>311</v>
       </c>
-      <c r="E29" s="49">
+      <c r="E29" s="52">
         <f>'PMF c0 round1-3'!E30+2</f>
         <v>317</v>
       </c>
-      <c r="F29" s="49">
+      <c r="F29" s="52">
         <f>'PMF c0 round1-3'!F30+2</f>
         <v>321</v>
       </c>
@@ -18985,11 +20661,11 @@
         <f>'PMF c0 round1-3'!D32</f>
         <v>351</v>
       </c>
-      <c r="E31" s="49">
+      <c r="E31" s="52">
         <f>'PMF c0 round1-3'!E32+2</f>
         <v>357</v>
       </c>
-      <c r="F31" s="49">
+      <c r="F31" s="52">
         <f>'PMF c0 round1-3'!F32+2</f>
         <v>361</v>
       </c>
@@ -19011,11 +20687,11 @@
         <f>'PMF c0 round1-3'!D33</f>
         <v>359</v>
       </c>
-      <c r="E32" s="49">
+      <c r="E32" s="52">
         <f>'PMF c0 round1-3'!E33+2</f>
         <v>365</v>
       </c>
-      <c r="F32" s="49">
+      <c r="F32" s="52">
         <f>'PMF c0 round1-3'!F33+2</f>
         <v>369</v>
       </c>
@@ -19037,11 +20713,11 @@
         <f>'PMF c0 round1-3'!D34</f>
         <v>367</v>
       </c>
-      <c r="E33" s="49">
+      <c r="E33" s="52">
         <f>'PMF c0 round1-3'!E34+2</f>
         <v>373</v>
       </c>
-      <c r="F33" s="49">
+      <c r="F33" s="52">
         <f>'PMF c0 round1-3'!F34+2</f>
         <v>377</v>
       </c>
@@ -19937,11 +21613,11 @@
         <f>C31+$Z$2</f>
         <v>287</v>
       </c>
-      <c r="E31" s="51">
+      <c r="E31" s="54">
         <f>D31+$AA$2+24</f>
         <v>303</v>
       </c>
-      <c r="F31" s="51">
+      <c r="F31" s="54">
         <f>E31+$AB$2</f>
         <v>319</v>
       </c>
